--- a/data/EVALUACIONES/FUERZA ANALITICA/DINAMOMETRIA_ANALITICO.xlsx
+++ b/data/EVALUACIONES/FUERZA ANALITICA/DINAMOMETRIA_ANALITICO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA ANALITICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65925B0-98E3-4C54-9631-3F7159F25E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD515699-19F5-416D-9FC7-CB29F8FCACB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="39">
   <si>
     <t>jingshuo_wang</t>
   </si>
@@ -43,9 +43,6 @@
   </si>
   <si>
     <t>ABD_Cadera_De_Pie_Derecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rodrigo_cueva </t>
   </si>
   <si>
     <t>Comments (set)</t>
@@ -96,16 +93,55 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Extension_rodilla_90_Derecha</t>
+    <t>Ikki_Muller_Salak</t>
   </si>
   <si>
-    <t>Flexion_rodilla_90_Derecha</t>
+    <t>Gonzalo_Kvisz</t>
   </si>
   <si>
-    <t>Flexion_rodilla_90_Izquierda</t>
+    <t>Alberto_Benedicto_Carpintero</t>
   </si>
   <si>
-    <t>Extension_rodilla_90_Izquierda</t>
+    <t>Alex_Palacios</t>
+  </si>
+  <si>
+    <t>Francisco_Javier_Marian_Medina</t>
+  </si>
+  <si>
+    <t>Javier_Caamano_Olmedo</t>
+  </si>
+  <si>
+    <t>Jorge_vicaria</t>
+  </si>
+  <si>
+    <t>Marco_Sanchez_Arias</t>
+  </si>
+  <si>
+    <t>Alex_Balbure</t>
+  </si>
+  <si>
+    <t>Ruben_Perez_Curto</t>
+  </si>
+  <si>
+    <t>Nicolas_Sustacha_Garate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juan_Manuel_Ruiz </t>
+  </si>
+  <si>
+    <t>Samuel_Chaparro_Garcia</t>
+  </si>
+  <si>
+    <t>Flexion_rodilla_90\u00BA_Derecha</t>
+  </si>
+  <si>
+    <t>Flexion_rodilla_90\u00BA_Izquierda</t>
+  </si>
+  <si>
+    <t>Extension_rodilla_90\u00BA_Derecha</t>
+  </si>
+  <si>
+    <t>Extension_rodilla_90\u00BA_Izquierda</t>
   </si>
 </sst>
 </file>
@@ -141,20 +177,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -170,12 +207,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}" name="Tabla1" displayName="Tabla1" ref="A1:P47" totalsRowShown="0">
-  <autoFilter ref="A1:P47" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}" name="Tabla1" displayName="Tabla1" ref="A1:P119" totalsRowShown="0">
+  <autoFilter ref="A1:P119" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{D8BDFCD4-5CB3-4377-9AAC-B345BFF21CCD}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{74190477-3FDA-4A91-AAD5-93B0F998FA90}" name="Date" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{EF7C01B4-3DD3-436A-AA24-BB5B8FE55AA0}" name="Time" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{74190477-3FDA-4A91-AAD5-93B0F998FA90}" name="Date" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{EF7C01B4-3DD3-436A-AA24-BB5B8FE55AA0}" name="Time" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{EDD40885-F2D2-4308-AED6-F4BAAE7E61A8}" name="Exercise"/>
     <tableColumn id="5" xr3:uid="{6F0E5AF9-E656-486A-ABBA-C00C3BE0F5C9}" name="Laterality"/>
     <tableColumn id="6" xr3:uid="{913730D9-54FF-46DC-A12C-BDCBE0564973}" name="Set"/>
@@ -491,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -512,66 +549,66 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C2" s="2">
         <v>0.66896990740740736</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>1</v>
@@ -583,7 +620,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>57.711316754652302</v>
+        <v>289.25587023221198</v>
       </c>
       <c r="I2">
         <v>56.8238073528996</v>
@@ -595,7 +632,7 @@
         <v>46.8252349035102</v>
       </c>
       <c r="L2">
-        <v>294.19647452857799</v>
+        <v>379.46032512658797</v>
       </c>
       <c r="M2">
         <v>19.031604767446499</v>
@@ -609,16 +646,16 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C3" s="2">
         <v>0.68237268518518523</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -630,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="H3">
-        <v>70.423064100850596</v>
+        <v>290.40810353633202</v>
       </c>
       <c r="I3">
         <v>65.197766604441</v>
@@ -641,8 +678,8 @@
       <c r="K3">
         <v>90.630564636909696</v>
       </c>
-      <c r="L3">
-        <v>35.363337681605799</v>
+      <c r="L3" s="3">
+        <v>-7.0148150136145E+28</v>
       </c>
       <c r="M3">
         <v>0.40207699784454998</v>
@@ -656,16 +693,16 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C4" s="2">
         <v>0.68259259259259264</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>1</v>
@@ -677,7 +714,7 @@
         <v>1</v>
       </c>
       <c r="H4">
-        <v>63.062872907414501</v>
+        <v>260.993407261801</v>
       </c>
       <c r="I4">
         <v>60.331909714106096</v>
@@ -689,7 +726,7 @@
         <v>61.724140696776701</v>
       </c>
       <c r="L4">
-        <v>302.93684098646901</v>
+        <v>577.045066866002</v>
       </c>
       <c r="M4">
         <v>8.8834383589549795</v>
@@ -703,16 +740,16 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C5" s="2">
         <v>0.68281250000000004</v>
       </c>
       <c r="D5" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>1</v>
@@ -724,7 +761,7 @@
         <v>1</v>
       </c>
       <c r="H5">
-        <v>67.375397011580603</v>
+        <v>262.24952922801799</v>
       </c>
       <c r="I5">
         <v>65.985944547827799</v>
@@ -736,7 +773,7 @@
         <v>66.0060379203439</v>
       </c>
       <c r="L5">
-        <v>151.04541621486101</v>
+        <v>744.55886206709602</v>
       </c>
       <c r="M5">
         <v>2.8030492326410501</v>
@@ -750,16 +787,16 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C6" s="2">
         <v>0.68297453703703703</v>
       </c>
       <c r="D6" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="E6" t="s">
         <v>1</v>
@@ -771,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>68.088844317134601</v>
+        <v>321.837330640049</v>
       </c>
       <c r="I6">
         <v>65.921659933341999</v>
@@ -783,7 +820,7 @@
         <v>64.9788573204237</v>
       </c>
       <c r="L6">
-        <v>396.43044797267498</v>
+        <v>645.241845575855</v>
       </c>
       <c r="M6">
         <v>16.4447934519382</v>
@@ -797,16 +834,16 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C7" s="2">
         <v>0.68343750000000003</v>
       </c>
       <c r="D7" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>1</v>
@@ -818,7 +855,7 @@
         <v>1</v>
       </c>
       <c r="H7">
-        <v>70.309197093867795</v>
+        <v>307.359868774012</v>
       </c>
       <c r="I7">
         <v>68.084511251677299</v>
@@ -830,7 +867,7 @@
         <v>68.157781003404494</v>
       </c>
       <c r="L7">
-        <v>195.86585943246999</v>
+        <v>865.051899143073</v>
       </c>
       <c r="M7">
         <v>3.7598318380487399</v>
@@ -844,16 +881,16 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C8" s="2">
         <v>0.68358796296296298</v>
       </c>
       <c r="D8" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
         <v>1</v>
@@ -865,7 +902,7 @@
         <v>1</v>
       </c>
       <c r="H8">
-        <v>69.680383787559606</v>
+        <v>302.49279743102301</v>
       </c>
       <c r="I8">
         <v>67.241000677082894</v>
@@ -877,7 +914,7 @@
         <v>66.361098873016701</v>
       </c>
       <c r="L8">
-        <v>379.611500779739</v>
+        <v>788.80450410320498</v>
       </c>
       <c r="M8">
         <v>13.0156161221567</v>
@@ -891,16 +928,16 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C9" s="2">
         <v>0.68385416666666665</v>
       </c>
       <c r="D9" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
         <v>1</v>
@@ -912,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="H9">
-        <v>61.299720950642097</v>
+        <v>286.05810551962799</v>
       </c>
       <c r="I9">
         <v>55.014207020772901</v>
@@ -924,7 +961,7 @@
         <v>54.5583903260884</v>
       </c>
       <c r="L9">
-        <v>134.485781187822</v>
+        <v>852.28966472971297</v>
       </c>
       <c r="M9">
         <v>3.0775724880036099</v>
@@ -938,16 +975,16 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B10" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C10" s="2">
         <v>0.68450231481481483</v>
       </c>
       <c r="D10" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
         <v>1</v>
@@ -959,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="H10">
-        <v>80.382504969279495</v>
+        <v>278.28849566886402</v>
       </c>
       <c r="I10">
         <v>76.265801414796798</v>
@@ -971,7 +1008,7 @@
         <v>75.734708265207004</v>
       </c>
       <c r="L10">
-        <v>265.720892332745</v>
+        <v>739.16569724590602</v>
       </c>
       <c r="M10">
         <v>4.9810132911129497</v>
@@ -985,16 +1022,16 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C11" s="2">
         <v>0.68484953703703699</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
         <v>1</v>
@@ -1006,7 +1043,7 @@
         <v>1</v>
       </c>
       <c r="H11">
-        <v>61.826757647976898</v>
+        <v>281.97597406809001</v>
       </c>
       <c r="I11">
         <v>57.5394058372557</v>
@@ -1018,7 +1055,7 @@
         <v>61.386682749189198</v>
       </c>
       <c r="L11">
-        <v>169.024859224431</v>
+        <v>1114.67283008355</v>
       </c>
       <c r="M11">
         <v>3.5517267559504999</v>
@@ -1032,16 +1069,16 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C12" s="2">
         <v>0.6849884259259259</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E12" t="s">
         <v>1</v>
@@ -1053,7 +1090,7 @@
         <v>1</v>
       </c>
       <c r="H12">
-        <v>71.145819544874897</v>
+        <v>296.87740248569497</v>
       </c>
       <c r="I12">
         <v>67.229042311017494</v>
@@ -1065,7 +1102,7 @@
         <v>69.171422135308305</v>
       </c>
       <c r="L12">
-        <v>183.474260248874</v>
+        <v>1238.4008602367901</v>
       </c>
       <c r="M12">
         <v>3.3818642449511498</v>
@@ -1079,16 +1116,16 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B13" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C13" s="2">
         <v>0.68520833333333331</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
         <v>1</v>
@@ -1100,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="H13">
-        <v>65.817340868061095</v>
+        <v>330.38177598207199</v>
       </c>
       <c r="I13">
         <v>63.540302184683902</v>
@@ -1112,7 +1149,7 @@
         <v>63.460538661638303</v>
       </c>
       <c r="L13">
-        <v>281.42915392641299</v>
+        <v>930.87873010261796</v>
       </c>
       <c r="M13">
         <v>7.2949455925108202</v>
@@ -1126,16 +1163,16 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B14" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C14" s="2">
         <v>0.68539351851851849</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
         <v>1</v>
@@ -1147,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="H14">
-        <v>78.059065266704394</v>
+        <v>338.71496479507402</v>
       </c>
       <c r="I14">
         <v>73.615156731600393</v>
@@ -1159,7 +1196,7 @@
         <v>75.952750582142997</v>
       </c>
       <c r="L14">
-        <v>311.94842807415898</v>
+        <v>455.21541467512401</v>
       </c>
       <c r="M14">
         <v>6.3819790512722498</v>
@@ -1173,16 +1210,16 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C15" s="2">
         <v>0.6856944444444445</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
         <v>1</v>
@@ -1194,7 +1231,7 @@
         <v>1</v>
       </c>
       <c r="H15">
-        <v>72.301132491354906</v>
+        <v>206.73610310663901</v>
       </c>
       <c r="I15">
         <v>70.940194222800898</v>
@@ -1206,7 +1243,7 @@
         <v>70.426907536767203</v>
       </c>
       <c r="L15">
-        <v>339.08662698797798</v>
+        <v>772.90812356524896</v>
       </c>
       <c r="M15">
         <v>8.5392578584853105</v>
@@ -1220,16 +1257,16 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C16" s="2">
         <v>0.68593749999999998</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E16" t="s">
         <v>1</v>
@@ -1241,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>73.490856865277607</v>
+        <v>193.68219721689499</v>
       </c>
       <c r="I16">
         <v>69.888547283056397</v>
@@ -1253,7 +1290,7 @@
         <v>70.355426881363201</v>
       </c>
       <c r="L16">
-        <v>254.22648231674299</v>
+        <v>538.04199927288596</v>
       </c>
       <c r="M16">
         <v>5.2061826747129798</v>
@@ -1267,16 +1304,16 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C17" s="2">
         <v>0.68667824074074069</v>
       </c>
       <c r="D17" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" t="s">
         <v>1</v>
@@ -1288,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="H17">
-        <v>94.535336429613807</v>
+        <v>220.32948135573301</v>
       </c>
       <c r="I17">
         <v>86.625756465048795</v>
@@ -1300,7 +1337,7 @@
         <v>86.583650618796597</v>
       </c>
       <c r="L17">
-        <v>467.527357639255</v>
+        <v>897.44655761257695</v>
       </c>
       <c r="M17">
         <v>11.0700610338037</v>
@@ -1314,10 +1351,10 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B18" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C18" s="2">
         <v>0.68687500000000001</v>
@@ -1335,7 +1372,7 @@
         <v>1</v>
       </c>
       <c r="H18">
-        <v>100.33329425540801</v>
+        <v>155.19411535616899</v>
       </c>
       <c r="I18">
         <v>87.590397481714803</v>
@@ -1347,7 +1384,7 @@
         <v>99.711657525245101</v>
       </c>
       <c r="L18">
-        <v>441.93390746428798</v>
+        <v>684.79660843400598</v>
       </c>
       <c r="M18">
         <v>7.2872070278993304</v>
@@ -1361,10 +1398,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B19" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C19" s="2">
         <v>0.68706018518518519</v>
@@ -1382,7 +1419,7 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>73.075633013698294</v>
+        <v>269.20193140466603</v>
       </c>
       <c r="I19">
         <v>68.660759127430893</v>
@@ -1394,7 +1431,7 @@
         <v>68.168738777279898</v>
       </c>
       <c r="L19">
-        <v>198.38863878477699</v>
+        <v>251.55676846441901</v>
       </c>
       <c r="M19">
         <v>3.82437806246715</v>
@@ -1408,16 +1445,16 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B20" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C20" s="2">
         <v>0.68723379629629633</v>
       </c>
       <c r="D20" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
         <v>1</v>
@@ -1429,7 +1466,7 @@
         <v>1</v>
       </c>
       <c r="H20">
-        <v>83.555914063649794</v>
+        <v>255.10218791135401</v>
       </c>
       <c r="I20">
         <v>81.395664078762195</v>
@@ -1441,7 +1478,7 @@
         <v>81.220052709267804</v>
       </c>
       <c r="L20">
-        <v>432.29529672075802</v>
+        <v>955.44222176287997</v>
       </c>
       <c r="M20">
         <v>10.675733922780401</v>
@@ -1455,16 +1492,16 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B21" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C21" s="2">
         <v>0.68739583333333332</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
         <v>1</v>
@@ -1476,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="H21">
-        <v>74.486320479893095</v>
+        <v>276.181541763849</v>
       </c>
       <c r="I21">
         <v>71.521568172164294</v>
@@ -1488,7 +1525,7 @@
         <v>70.940185281625006</v>
       </c>
       <c r="L21">
-        <v>390.89372160156199</v>
+        <v>935.443266057286</v>
       </c>
       <c r="M21">
         <v>11.6782652623472</v>
@@ -1502,16 +1539,16 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B22" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C22" s="2">
         <v>0.68761574074074072</v>
       </c>
       <c r="D22" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E22" t="s">
         <v>1</v>
@@ -1523,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="H22">
-        <v>81.588772728344196</v>
+        <v>262.20863472877602</v>
       </c>
       <c r="I22">
         <v>78.960967592186705</v>
@@ -1535,7 +1572,7 @@
         <v>83.013978613382903</v>
       </c>
       <c r="L22">
-        <v>139.24905703022</v>
+        <v>652.50809054022295</v>
       </c>
       <c r="M22">
         <v>1.93222966107956</v>
@@ -1549,16 +1586,16 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C23" s="2">
         <v>0.68783564814814813</v>
       </c>
       <c r="D23" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E23" t="s">
         <v>1</v>
@@ -1570,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="H23">
-        <v>77.217915305442304</v>
+        <v>183.477642835138</v>
       </c>
       <c r="I23">
         <v>72.970428641746807</v>
@@ -1582,7 +1619,7 @@
         <v>73.1627981602755</v>
       </c>
       <c r="L23">
-        <v>224.604432264428</v>
+        <v>548.21551265805203</v>
       </c>
       <c r="M23">
         <v>4.11394755029142</v>
@@ -1596,16 +1633,16 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>46232</v>
+        <v>46247</v>
       </c>
       <c r="C24" s="2">
         <v>0.6880208333333333</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
         <v>1</v>
@@ -1617,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="H24">
-        <v>80.419172894075402</v>
+        <v>175.86876396265001</v>
       </c>
       <c r="I24">
         <v>75.642473587838893</v>
@@ -1629,7 +1666,7 @@
         <v>73.754567256993099</v>
       </c>
       <c r="L24">
-        <v>238.54929370723599</v>
+        <v>190.96028010655201</v>
       </c>
       <c r="M24">
         <v>4.42592876614719</v>
@@ -1643,10 +1680,10 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C25" s="2">
         <v>0.66896990740740736</v>
@@ -1664,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="H25">
-        <v>57.711316754652302</v>
+        <v>169.17884302337299</v>
       </c>
       <c r="I25">
         <v>56.8238073528996</v>
@@ -1675,9 +1712,6 @@
       <c r="K25">
         <v>46.8252349035102</v>
       </c>
-      <c r="L25">
-        <v>294.19647452857799</v>
-      </c>
       <c r="M25">
         <v>19.031604767446499</v>
       </c>
@@ -1690,16 +1724,16 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C26" s="2">
         <v>0.68237268518518523</v>
       </c>
       <c r="D26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" t="s">
         <v>1</v>
@@ -1711,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="H26">
-        <v>70.423064100850596</v>
+        <v>172.27100469440299</v>
       </c>
       <c r="I26">
         <v>65.197766604441</v>
@@ -1723,7 +1757,7 @@
         <v>90.630564636909696</v>
       </c>
       <c r="L26">
-        <v>35.363337681605799</v>
+        <v>167.36611891939401</v>
       </c>
       <c r="M26">
         <v>0.40207699784454998</v>
@@ -1737,16 +1771,16 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B27" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C27" s="2">
         <v>0.68259259259259264</v>
       </c>
       <c r="D27" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E27" t="s">
         <v>1</v>
@@ -1758,7 +1792,7 @@
         <v>1</v>
       </c>
       <c r="H27">
-        <v>63.062872907414501</v>
+        <v>253.662325685898</v>
       </c>
       <c r="I27">
         <v>60.331909714106096</v>
@@ -1770,7 +1804,7 @@
         <v>61.724140696776701</v>
       </c>
       <c r="L27">
-        <v>302.93684098646901</v>
+        <v>944.58178356615394</v>
       </c>
       <c r="M27">
         <v>8.8834383589549795</v>
@@ -1784,16 +1818,16 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B28" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C28" s="2">
         <v>0.68281250000000004</v>
       </c>
       <c r="D28" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" t="s">
         <v>1</v>
@@ -1805,7 +1839,7 @@
         <v>1</v>
       </c>
       <c r="H28">
-        <v>67.375397011580603</v>
+        <v>181.990770138578</v>
       </c>
       <c r="I28">
         <v>65.985944547827799</v>
@@ -1817,7 +1851,7 @@
         <v>66.0060379203439</v>
       </c>
       <c r="L28">
-        <v>151.04541621486101</v>
+        <v>693.555629759775</v>
       </c>
       <c r="M28">
         <v>2.8030492326410501</v>
@@ -1831,16 +1865,16 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B29" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C29" s="2">
         <v>0.68297453703703703</v>
       </c>
       <c r="D29" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E29" t="s">
         <v>1</v>
@@ -1852,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="H29">
-        <v>68.088844317134601</v>
+        <v>305.44775512179302</v>
       </c>
       <c r="I29">
         <v>65.921659933341999</v>
@@ -1864,7 +1898,7 @@
         <v>64.9788573204237</v>
       </c>
       <c r="L29">
-        <v>396.43044797267498</v>
+        <v>500.90380502457498</v>
       </c>
       <c r="M29">
         <v>16.4447934519382</v>
@@ -1878,16 +1912,16 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B30" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C30" s="2">
         <v>0.68343750000000003</v>
       </c>
       <c r="D30" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" t="s">
         <v>1</v>
@@ -1899,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="H30">
-        <v>70.309197093867795</v>
+        <v>77.099259002155193</v>
       </c>
       <c r="I30">
         <v>68.084511251677299</v>
@@ -1910,9 +1944,6 @@
       <c r="K30">
         <v>68.157781003404494</v>
       </c>
-      <c r="L30">
-        <v>195.86585943246999</v>
-      </c>
       <c r="M30">
         <v>3.7598318380487399</v>
       </c>
@@ -1925,16 +1956,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B31" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C31" s="2">
         <v>0.68358796296296298</v>
       </c>
       <c r="D31" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="E31" t="s">
         <v>1</v>
@@ -1946,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="H31">
-        <v>69.680383787559606</v>
+        <v>452.61610194763301</v>
       </c>
       <c r="I31">
         <v>67.241000677082894</v>
@@ -1958,7 +1989,7 @@
         <v>66.361098873016701</v>
       </c>
       <c r="L31">
-        <v>379.611500779739</v>
+        <v>712.76072516122804</v>
       </c>
       <c r="M31">
         <v>13.0156161221567</v>
@@ -1972,16 +2003,16 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B32" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C32" s="2">
         <v>0.68385416666666665</v>
       </c>
       <c r="D32" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
         <v>1</v>
@@ -1993,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="H32">
-        <v>61.299720950642097</v>
+        <v>437.87886237248102</v>
       </c>
       <c r="I32">
         <v>55.014207020772901</v>
@@ -2005,7 +2036,7 @@
         <v>54.5583903260884</v>
       </c>
       <c r="L32">
-        <v>134.485781187822</v>
+        <v>874.68049400842904</v>
       </c>
       <c r="M32">
         <v>3.0775724880036099</v>
@@ -2019,16 +2050,16 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B33" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C33" s="2">
         <v>0.68450231481481483</v>
       </c>
       <c r="D33" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E33" t="s">
         <v>1</v>
@@ -2040,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="H33">
-        <v>80.382504969279495</v>
+        <v>516.34935110781396</v>
       </c>
       <c r="I33">
         <v>76.265801414796798</v>
@@ -2052,7 +2083,7 @@
         <v>75.734708265207004</v>
       </c>
       <c r="L33">
-        <v>265.720892332745</v>
+        <v>1090.06330871809</v>
       </c>
       <c r="M33">
         <v>4.9810132911129497</v>
@@ -2066,16 +2097,16 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B34" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C34" s="2">
         <v>0.68484953703703699</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
         <v>1</v>
@@ -2087,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="H34">
-        <v>61.826757647976898</v>
+        <v>541.07073811590794</v>
       </c>
       <c r="I34">
         <v>57.5394058372557</v>
@@ -2099,7 +2130,7 @@
         <v>61.386682749189198</v>
       </c>
       <c r="L34">
-        <v>169.024859224431</v>
+        <v>1093.7015305636501</v>
       </c>
       <c r="M34">
         <v>3.5517267559504999</v>
@@ -2113,16 +2144,16 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B35" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C35" s="2">
         <v>0.6849884259259259</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E35" t="s">
         <v>1</v>
@@ -2134,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="H35">
-        <v>71.145819544874897</v>
+        <v>354.99597997651301</v>
       </c>
       <c r="I35">
         <v>67.229042311017494</v>
@@ -2146,7 +2177,7 @@
         <v>69.171422135308305</v>
       </c>
       <c r="L35">
-        <v>183.474260248874</v>
+        <v>1189.4756031808199</v>
       </c>
       <c r="M35">
         <v>3.3818642449511498</v>
@@ -2160,16 +2191,16 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B36" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C36" s="2">
         <v>0.68520833333333331</v>
       </c>
       <c r="D36" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E36" t="s">
         <v>1</v>
@@ -2181,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>65.817340868061095</v>
+        <v>456.246040300733</v>
       </c>
       <c r="I36">
         <v>63.540302184683902</v>
@@ -2193,7 +2224,7 @@
         <v>63.460538661638303</v>
       </c>
       <c r="L36">
-        <v>281.42915392641299</v>
+        <v>1466.3363982073499</v>
       </c>
       <c r="M36">
         <v>7.2949455925108202</v>
@@ -2207,16 +2238,16 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B37" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C37" s="2">
         <v>0.68539351851851849</v>
       </c>
       <c r="D37" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E37" t="s">
         <v>1</v>
@@ -2228,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="H37">
-        <v>78.059065266704394</v>
+        <v>540.99161873109301</v>
       </c>
       <c r="I37">
         <v>73.615156731600393</v>
@@ -2240,7 +2271,7 @@
         <v>75.952750582142997</v>
       </c>
       <c r="L37">
-        <v>311.94842807415898</v>
+        <v>1284.2555750802501</v>
       </c>
       <c r="M37">
         <v>6.3819790512722498</v>
@@ -2254,16 +2285,16 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B38" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C38" s="2">
         <v>0.6856944444444445</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E38" t="s">
         <v>1</v>
@@ -2275,7 +2306,7 @@
         <v>1</v>
       </c>
       <c r="H38">
-        <v>72.301132491354906</v>
+        <v>589.24878634687002</v>
       </c>
       <c r="I38">
         <v>70.940194222800898</v>
@@ -2287,7 +2318,7 @@
         <v>70.426907536767203</v>
       </c>
       <c r="L38">
-        <v>339.08662698797798</v>
+        <v>1169.8698332127601</v>
       </c>
       <c r="M38">
         <v>8.5392578584853105</v>
@@ -2301,16 +2332,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B39" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C39" s="2">
         <v>0.68593749999999998</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E39" t="s">
         <v>1</v>
@@ -2322,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="H39">
-        <v>73.490856865277607</v>
+        <v>194.32365381184499</v>
       </c>
       <c r="I39">
         <v>69.888547283056397</v>
@@ -2334,7 +2365,7 @@
         <v>70.355426881363201</v>
       </c>
       <c r="L39">
-        <v>254.22648231674299</v>
+        <v>1252.28793795447</v>
       </c>
       <c r="M39">
         <v>5.2061826747129798</v>
@@ -2348,16 +2379,16 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B40" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C40" s="2">
         <v>0.68667824074074069</v>
       </c>
       <c r="D40" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="E40" t="s">
         <v>1</v>
@@ -2369,7 +2400,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>94.535336429613807</v>
+        <v>284.64919674340001</v>
       </c>
       <c r="I40">
         <v>86.625756465048795</v>
@@ -2381,7 +2412,7 @@
         <v>86.583650618796597</v>
       </c>
       <c r="L40">
-        <v>467.527357639255</v>
+        <v>693.44873977700695</v>
       </c>
       <c r="M40">
         <v>11.0700610338037</v>
@@ -2395,16 +2426,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B41" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C41" s="2">
         <v>0.68687500000000001</v>
       </c>
       <c r="D41" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
         <v>1</v>
@@ -2416,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="H41">
-        <v>100.33329425540801</v>
+        <v>158.77410557019601</v>
       </c>
       <c r="I41">
         <v>87.590397481714803</v>
@@ -2427,9 +2458,6 @@
       <c r="K41">
         <v>99.711657525245101</v>
       </c>
-      <c r="L41">
-        <v>441.93390746428798</v>
-      </c>
       <c r="M41">
         <v>7.2872070278993304</v>
       </c>
@@ -2442,16 +2470,16 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B42" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C42" s="2">
         <v>0.68706018518518519</v>
       </c>
       <c r="D42" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="s">
         <v>1</v>
@@ -2463,7 +2491,7 @@
         <v>1</v>
       </c>
       <c r="H42">
-        <v>73.075633013698294</v>
+        <v>199.796437973835</v>
       </c>
       <c r="I42">
         <v>68.660759127430893</v>
@@ -2475,7 +2503,7 @@
         <v>68.168738777279898</v>
       </c>
       <c r="L42">
-        <v>198.38863878477699</v>
+        <v>1290.8932313727501</v>
       </c>
       <c r="M42">
         <v>3.82437806246715</v>
@@ -2489,16 +2517,16 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B43" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C43" s="2">
         <v>0.68723379629629633</v>
       </c>
       <c r="D43" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E43" t="s">
         <v>1</v>
@@ -2510,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="H43">
-        <v>83.555914063649794</v>
+        <v>161.82188748652399</v>
       </c>
       <c r="I43">
         <v>81.395664078762195</v>
@@ -2522,7 +2550,7 @@
         <v>81.220052709267804</v>
       </c>
       <c r="L43">
-        <v>432.29529672075802</v>
+        <v>1118.7506591245201</v>
       </c>
       <c r="M43">
         <v>10.675733922780401</v>
@@ -2536,16 +2564,16 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B44" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C44" s="2">
         <v>0.68739583333333332</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
         <v>1</v>
@@ -2557,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="H44">
-        <v>74.486320479893095</v>
+        <v>178.76463249610001</v>
       </c>
       <c r="I44">
         <v>71.521568172164294</v>
@@ -2569,7 +2597,7 @@
         <v>70.940185281625006</v>
       </c>
       <c r="L44">
-        <v>390.89372160156199</v>
+        <v>1242.25360723616</v>
       </c>
       <c r="M44">
         <v>11.6782652623472</v>
@@ -2583,16 +2611,16 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B45" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C45" s="2">
         <v>0.68761574074074072</v>
       </c>
       <c r="D45" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E45" t="s">
         <v>1</v>
@@ -2604,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="H45">
-        <v>81.588772728344196</v>
+        <v>180.79037691030399</v>
       </c>
       <c r="I45">
         <v>78.960967592186705</v>
@@ -2616,7 +2644,7 @@
         <v>83.013978613382903</v>
       </c>
       <c r="L45">
-        <v>139.24905703022</v>
+        <v>739.29483630878599</v>
       </c>
       <c r="M45">
         <v>1.93222966107956</v>
@@ -2630,16 +2658,16 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B46" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C46" s="2">
         <v>0.68783564814814813</v>
       </c>
       <c r="D46" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
         <v>1</v>
@@ -2651,7 +2679,7 @@
         <v>1</v>
       </c>
       <c r="H46">
-        <v>3.2179153054423</v>
+        <v>236.07431460472699</v>
       </c>
       <c r="I46">
         <v>72.970428641746807</v>
@@ -2663,7 +2691,7 @@
         <v>73.1627981602755</v>
       </c>
       <c r="L46">
-        <v>224.604432264428</v>
+        <v>507.94850896611501</v>
       </c>
       <c r="M46">
         <v>4.11394755029142</v>
@@ -2677,16 +2705,16 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B47" s="1">
-        <v>46297</v>
+        <v>46247</v>
       </c>
       <c r="C47" s="2">
         <v>0.6880208333333333</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E47" t="s">
         <v>1</v>
@@ -2698,7 +2726,7 @@
         <v>1</v>
       </c>
       <c r="H47">
-        <v>80.419172894075402</v>
+        <v>205.414238166654</v>
       </c>
       <c r="I47">
         <v>75.642473587838893</v>
@@ -2710,7 +2738,7 @@
         <v>73.754567256993099</v>
       </c>
       <c r="L47">
-        <v>238.54929370723599</v>
+        <v>1137.80370939927</v>
       </c>
       <c r="M47">
         <v>4.42592876614719</v>
@@ -2720,6 +2748,1293 @@
       </c>
       <c r="O47">
         <v>3.4026037055172602</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48">
+        <v>144.37411977902599</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>193.43378534266699</v>
+      </c>
+      <c r="L49">
+        <v>188.42571810457201</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>26</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50">
+        <v>176.321505645765</v>
+      </c>
+      <c r="L50">
+        <v>1070.88170097181</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s">
+        <v>35</v>
+      </c>
+      <c r="H51">
+        <v>135.82066962637401</v>
+      </c>
+      <c r="L51">
+        <v>746.60173289408101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s">
+        <v>36</v>
+      </c>
+      <c r="H52">
+        <v>203.67206036466101</v>
+      </c>
+      <c r="L52">
+        <v>336.40634358601397</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s">
+        <v>3</v>
+      </c>
+      <c r="H53">
+        <v>255.82233283162901</v>
+      </c>
+      <c r="L53">
+        <v>1332.45217041909</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54">
+        <v>194.463615565032</v>
+      </c>
+      <c r="L54">
+        <v>1346.9112306105301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s">
+        <v>2</v>
+      </c>
+      <c r="H55">
+        <v>186.24094010229399</v>
+      </c>
+      <c r="L55">
+        <v>765.13706484240402</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s">
+        <v>4</v>
+      </c>
+      <c r="H56">
+        <v>206.31038845646799</v>
+      </c>
+      <c r="L56">
+        <v>1271.32539016743</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s">
+        <v>37</v>
+      </c>
+      <c r="H57">
+        <v>285.399348863066</v>
+      </c>
+      <c r="L57">
+        <v>1214.7445873828599</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s">
+        <v>38</v>
+      </c>
+      <c r="H58">
+        <v>254.25659617779701</v>
+      </c>
+      <c r="L58">
+        <v>1335.80610380843</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s">
+        <v>37</v>
+      </c>
+      <c r="H59">
+        <v>487.70941201555001</v>
+      </c>
+      <c r="L59">
+        <v>1347.5335731294899</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s">
+        <v>38</v>
+      </c>
+      <c r="H60">
+        <v>574.48955280392602</v>
+      </c>
+      <c r="L60">
+        <v>2405.4168622206898</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s">
+        <v>37</v>
+      </c>
+      <c r="H61">
+        <v>186.775756871423</v>
+      </c>
+      <c r="L61">
+        <v>836.54920600734704</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s">
+        <v>38</v>
+      </c>
+      <c r="H62">
+        <v>185.44821179498001</v>
+      </c>
+      <c r="L62">
+        <v>755.08235736881704</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>28</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s">
+        <v>35</v>
+      </c>
+      <c r="H63">
+        <v>323.89606271525798</v>
+      </c>
+      <c r="L63">
+        <v>1101.85415436877</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>28</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s">
+        <v>36</v>
+      </c>
+      <c r="H64">
+        <v>343.074145341041</v>
+      </c>
+      <c r="L64">
+        <v>1156.7315372191099</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s">
+        <v>3</v>
+      </c>
+      <c r="H65">
+        <v>154.344350536641</v>
+      </c>
+      <c r="L65">
+        <v>1036.0907179804301</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>28</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66">
+        <v>221.899547954925</v>
+      </c>
+      <c r="L66">
+        <v>1039.9921642826801</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>28</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67">
+        <v>167.04643137153599</v>
+      </c>
+      <c r="L67">
+        <v>1045.3357573005901</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>28</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68">
+        <v>213.95366223602301</v>
+      </c>
+      <c r="L68">
+        <v>947.68789759652805</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>29</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s">
+        <v>35</v>
+      </c>
+      <c r="H69">
+        <v>168.87268460100699</v>
+      </c>
+      <c r="L69">
+        <v>18.0022053657184</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>29</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s">
+        <v>36</v>
+      </c>
+      <c r="H70">
+        <v>140.48957688096999</v>
+      </c>
+      <c r="L70">
+        <v>526.68558465019998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>29</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s">
+        <v>3</v>
+      </c>
+      <c r="H71">
+        <v>127.42640102186201</v>
+      </c>
+      <c r="L71">
+        <v>597.17029269262105</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72">
+        <v>139.791646502916</v>
+      </c>
+      <c r="L72">
+        <v>748.05326371848003</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s">
+        <v>4</v>
+      </c>
+      <c r="H73">
+        <v>135.39181024553</v>
+      </c>
+      <c r="L73">
+        <v>784.34952174150601</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>29</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s">
+        <v>2</v>
+      </c>
+      <c r="H74">
+        <v>91.754979017412396</v>
+      </c>
+      <c r="L74">
+        <v>462.63081258683098</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>29</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s">
+        <v>37</v>
+      </c>
+      <c r="H75">
+        <v>207.50756856236299</v>
+      </c>
+      <c r="L75">
+        <v>315.21634585677401</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>29</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s">
+        <v>38</v>
+      </c>
+      <c r="H76">
+        <v>275.95332144227302</v>
+      </c>
+      <c r="L76">
+        <v>597.332609627686</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s">
+        <v>3</v>
+      </c>
+      <c r="H77">
+        <v>259.52012147360699</v>
+      </c>
+      <c r="L77">
+        <v>892.92983544509298</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s">
+        <v>5</v>
+      </c>
+      <c r="H78">
+        <v>174.301993760285</v>
+      </c>
+      <c r="L78">
+        <v>1198.5885708216299</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s">
+        <v>4</v>
+      </c>
+      <c r="H79">
+        <v>198.183594144555</v>
+      </c>
+      <c r="L79">
+        <v>1332.4061302279299</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s">
+        <v>2</v>
+      </c>
+      <c r="H80">
+        <v>240.35464024935899</v>
+      </c>
+      <c r="L80">
+        <v>1146.6979485320201</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>28</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s">
+        <v>37</v>
+      </c>
+      <c r="H81">
+        <v>391.77702352852998</v>
+      </c>
+      <c r="L81">
+        <v>880.01344198444701</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s">
+        <v>35</v>
+      </c>
+      <c r="H82">
+        <v>234.74759355253599</v>
+      </c>
+      <c r="L82">
+        <v>1415.4735006865899</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s">
+        <v>36</v>
+      </c>
+      <c r="H83">
+        <v>248.05463289630299</v>
+      </c>
+      <c r="L83">
+        <v>1647.9369562182001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>28</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s">
+        <v>38</v>
+      </c>
+      <c r="H84">
+        <v>533.34955497838598</v>
+      </c>
+      <c r="L84" s="3">
+        <v>-1.01930822864721E+30</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s">
+        <v>37</v>
+      </c>
+      <c r="H85">
+        <v>358.61937049900598</v>
+      </c>
+      <c r="L85">
+        <v>900.291177480584</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B86" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s">
+        <v>38</v>
+      </c>
+      <c r="H86">
+        <v>294.44187771783299</v>
+      </c>
+      <c r="L86">
+        <v>1684.5291541822701</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s">
+        <v>38</v>
+      </c>
+      <c r="H87">
+        <v>348.02439952114599</v>
+      </c>
+      <c r="L87">
+        <v>541.65076606346804</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B88" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s">
+        <v>37</v>
+      </c>
+      <c r="H88">
+        <v>289.418650785789</v>
+      </c>
+      <c r="L88">
+        <v>348.37986024774301</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s">
+        <v>37</v>
+      </c>
+      <c r="H89">
+        <v>394.62818721071102</v>
+      </c>
+      <c r="L89">
+        <v>2565.2096550433898</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s">
+        <v>38</v>
+      </c>
+      <c r="H90">
+        <v>495.12366719147798</v>
+      </c>
+      <c r="L90">
+        <v>1919.8058948543301</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>33</v>
+      </c>
+      <c r="B91" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s">
+        <v>38</v>
+      </c>
+      <c r="H91">
+        <v>638.05849410390204</v>
+      </c>
+      <c r="L91">
+        <v>1276.3123983437499</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>33</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s">
+        <v>37</v>
+      </c>
+      <c r="H92">
+        <v>369.07202765014398</v>
+      </c>
+      <c r="L92">
+        <v>1637.7622036288899</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>34</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s">
+        <v>38</v>
+      </c>
+      <c r="H93">
+        <v>137.068041477619</v>
+      </c>
+      <c r="L93">
+        <v>464.25480152752601</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>34</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s">
+        <v>37</v>
+      </c>
+      <c r="H94">
+        <v>243.46135286167899</v>
+      </c>
+      <c r="L94">
+        <v>320.26247018007899</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s">
+        <v>36</v>
+      </c>
+      <c r="H95">
+        <v>162.58819555391</v>
+      </c>
+      <c r="L95">
+        <v>959.37470863552005</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>31</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s">
+        <v>35</v>
+      </c>
+      <c r="H96">
+        <v>172.63177491649699</v>
+      </c>
+      <c r="L96">
+        <v>864.00344262149201</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>32</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s">
+        <v>36</v>
+      </c>
+      <c r="H97">
+        <v>197.611116773492</v>
+      </c>
+      <c r="L97">
+        <v>1175.25050819066</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s">
+        <v>35</v>
+      </c>
+      <c r="H98">
+        <v>199.668812967251</v>
+      </c>
+      <c r="L98">
+        <v>1336.71834206021</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s">
+        <v>35</v>
+      </c>
+      <c r="H99">
+        <v>166.27433274294299</v>
+      </c>
+      <c r="L99">
+        <v>918.992476753593</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>33</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s">
+        <v>36</v>
+      </c>
+      <c r="H100">
+        <v>266.04587760875199</v>
+      </c>
+      <c r="L100">
+        <v>250.73044563827699</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s">
+        <v>35</v>
+      </c>
+      <c r="H101">
+        <v>93.533578225030098</v>
+      </c>
+      <c r="L101">
+        <v>222.732204039501</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>34</v>
+      </c>
+      <c r="B102" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s">
+        <v>36</v>
+      </c>
+      <c r="H102">
+        <v>136.44298772302699</v>
+      </c>
+      <c r="L102">
+        <v>127.63819815730599</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>31</v>
+      </c>
+      <c r="B103" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s">
+        <v>3</v>
+      </c>
+      <c r="H103">
+        <v>150.51104005821199</v>
+      </c>
+      <c r="L103">
+        <v>987.90428201393695</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>31</v>
+      </c>
+      <c r="B104" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s">
+        <v>5</v>
+      </c>
+      <c r="H104">
+        <v>114.45874801253601</v>
+      </c>
+      <c r="L104">
+        <v>670.40597859371201</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>31</v>
+      </c>
+      <c r="B105" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s">
+        <v>2</v>
+      </c>
+      <c r="H105">
+        <v>185.30216638166999</v>
+      </c>
+      <c r="L105">
+        <v>925.36525777901704</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>31</v>
+      </c>
+      <c r="B106" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s">
+        <v>4</v>
+      </c>
+      <c r="H106">
+        <v>119.59182620434299</v>
+      </c>
+      <c r="L106">
+        <v>443.09740034904303</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>32</v>
+      </c>
+      <c r="B107" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s">
+        <v>3</v>
+      </c>
+      <c r="H107">
+        <v>224.68302121025701</v>
+      </c>
+      <c r="L107">
+        <v>1207.3492977439701</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>32</v>
+      </c>
+      <c r="B108" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s">
+        <v>5</v>
+      </c>
+      <c r="H108">
+        <v>194.466704596288</v>
+      </c>
+      <c r="L108">
+        <v>1272.57277576974</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>32</v>
+      </c>
+      <c r="B109" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s">
+        <v>2</v>
+      </c>
+      <c r="H109">
+        <v>209.153101333287</v>
+      </c>
+      <c r="L109">
+        <v>1217.59296523392</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>32</v>
+      </c>
+      <c r="B110" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s">
+        <v>4</v>
+      </c>
+      <c r="H110">
+        <v>172.13383734504501</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>33</v>
+      </c>
+      <c r="B111" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s">
+        <v>3</v>
+      </c>
+      <c r="H111">
+        <v>167.23212784208599</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>33</v>
+      </c>
+      <c r="B112" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s">
+        <v>3</v>
+      </c>
+      <c r="H112">
+        <v>129.544432205063</v>
+      </c>
+      <c r="L112">
+        <v>422.922647919886</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>33</v>
+      </c>
+      <c r="B113" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s">
+        <v>5</v>
+      </c>
+      <c r="H113">
+        <v>151.15603715980399</v>
+      </c>
+      <c r="L113">
+        <v>706.84626676823405</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>33</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s">
+        <v>2</v>
+      </c>
+      <c r="H114">
+        <v>147.72051099000001</v>
+      </c>
+      <c r="L114">
+        <v>57.578708711607298</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>33</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s">
+        <v>4</v>
+      </c>
+      <c r="H115">
+        <v>152.76703922515699</v>
+      </c>
+      <c r="L115">
+        <v>532.19822373433601</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>34</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s">
+        <v>3</v>
+      </c>
+      <c r="H116">
+        <v>141.90403350396801</v>
+      </c>
+      <c r="L116">
+        <v>661.02793295996298</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>34</v>
+      </c>
+      <c r="B117" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s">
+        <v>4</v>
+      </c>
+      <c r="H117">
+        <v>121.29977436612999</v>
+      </c>
+      <c r="L117">
+        <v>113.65274010442</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s">
+        <v>2</v>
+      </c>
+      <c r="H118">
+        <v>121.83743308515299</v>
+      </c>
+      <c r="L118">
+        <v>390.13215870333801</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s">
+        <v>5</v>
+      </c>
+      <c r="H119">
+        <v>150.296595967196</v>
+      </c>
+      <c r="L119">
+        <v>453.872127357061</v>
       </c>
     </row>
   </sheetData>

--- a/data/EVALUACIONES/FUERZA ANALITICA/DINAMOMETRIA_ANALITICO.xlsx
+++ b/data/EVALUACIONES/FUERZA ANALITICA/DINAMOMETRIA_ANALITICO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA ANALITICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD515699-19F5-416D-9FC7-CB29F8FCACB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0C60DA-5A79-45A8-B04A-688C90FBEA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="52">
   <si>
     <t>jingshuo_wang</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>Model K</t>
-  </si>
-  <si>
-    <t>RFD_FITTED_BEST_AVG_RFD_IN_X_MS_150_-1</t>
   </si>
   <si>
     <t>MaxForce (model)</t>
@@ -143,6 +140,48 @@
   <si>
     <t>Extension_rodilla_90\u00BA_Izquierda</t>
   </si>
+  <si>
+    <t>Jaime_Munoz_Garcia</t>
+  </si>
+  <si>
+    <t>Carlos_De_La_Fe_Simon</t>
+  </si>
+  <si>
+    <t>Mariano_Blazquez_Valles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presley_Osarenkhoe </t>
+  </si>
+  <si>
+    <t>Guillermo_Garcia_Lapena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rodrigo_cueva </t>
+  </si>
+  <si>
+    <t>Rodri_Sanchez_Ramos</t>
+  </si>
+  <si>
+    <t>Daniel_Diaz_Alvaro</t>
+  </si>
+  <si>
+    <t>Petko_Avramov</t>
+  </si>
+  <si>
+    <t>Dennis_Medina</t>
+  </si>
+  <si>
+    <t>Luis_Moliner</t>
+  </si>
+  <si>
+    <t>Alejandro_Garcia_Gumiel</t>
+  </si>
+  <si>
+    <t>Noah_Ojo_Barranco</t>
+  </si>
+  <si>
+    <t>Gonzalo_Echavarria</t>
+  </si>
 </sst>
 </file>
 
@@ -157,15 +196,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -173,25 +218,96 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="26" formatCode="h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -207,21 +323,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}" name="Tabla1" displayName="Tabla1" ref="A1:P119" totalsRowShown="0">
-  <autoFilter ref="A1:P119" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}"/>
-  <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{D8BDFCD4-5CB3-4377-9AAC-B345BFF21CCD}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{74190477-3FDA-4A91-AAD5-93B0F998FA90}" name="Date" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{EF7C01B4-3DD3-436A-AA24-BB5B8FE55AA0}" name="Time" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{EDD40885-F2D2-4308-AED6-F4BAAE7E61A8}" name="Exercise"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}" name="Tabla1" displayName="Tabla1" ref="A1:O229" totalsRowShown="0">
+  <autoFilter ref="A1:O229" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{D8BDFCD4-5CB3-4377-9AAC-B345BFF21CCD}" name="Name" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{74190477-3FDA-4A91-AAD5-93B0F998FA90}" name="Date" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{EF7C01B4-3DD3-436A-AA24-BB5B8FE55AA0}" name="Time" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{EDD40885-F2D2-4308-AED6-F4BAAE7E61A8}" name="Exercise" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{6F0E5AF9-E656-486A-ABBA-C00C3BE0F5C9}" name="Laterality"/>
     <tableColumn id="6" xr3:uid="{913730D9-54FF-46DC-A12C-BDCBE0564973}" name="Set"/>
     <tableColumn id="7" xr3:uid="{C12057EB-5F4A-4A63-99B6-10BE98BAF73E}" name="Repetition"/>
-    <tableColumn id="8" xr3:uid="{9B602B7A-E02E-4370-B7D5-7F13C6D2F564}" name="MaxForce (raw)"/>
+    <tableColumn id="8" xr3:uid="{9B602B7A-E02E-4370-B7D5-7F13C6D2F564}" name="MaxForce (raw)" dataDxfId="0"/>
     <tableColumn id="9" xr3:uid="{78DE544A-D252-45FE-B588-E8E1C3B56561}" name="Max AVG Force in 1 s (raw)"/>
     <tableColumn id="10" xr3:uid="{C92CDA2B-5D5B-40F8-B482-0E9DEA5E2BEA}" name="Best stability in 1 s (raw)"/>
     <tableColumn id="11" xr3:uid="{4DC9D655-350E-47AA-BA52-6A65EC289947}" name="MaxForce (model)"/>
-    <tableColumn id="12" xr3:uid="{EC415618-A56C-428F-966E-12B6981D364D}" name="RFD_FITTED_BEST_AVG_RFD_IN_X_MS_150_-1"/>
     <tableColumn id="13" xr3:uid="{23DB21BE-0EBA-42AC-A44C-AA4D6EE03D5C}" name="Model K"/>
     <tableColumn id="14" xr3:uid="{3EC9600E-E1D1-4688-92D2-A1B1DAE564FD}" name="Model Tau"/>
     <tableColumn id="15" xr3:uid="{E9368C37-84F7-473F-82DF-8649683CFE4D}" name="Model mean error (%)"/>
@@ -528,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FF0B100-72AE-4E6A-8897-D79B621AF892}">
-  <dimension ref="A1:P119"/>
+  <dimension ref="A1:O229"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
@@ -540,66 +655,62 @@
     <col min="9" max="9" width="27.77734375" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="25.5546875" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="20" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="44.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="0" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="11.88671875" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="21.33203125" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="16.21875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="21.33203125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="16.21875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>9</v>
-      </c>
-      <c r="N1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>22</v>
       </c>
       <c r="B2" s="1">
         <v>46247</v>
@@ -607,8 +718,8 @@
       <c r="C2" s="2">
         <v>0.66896990740740736</v>
       </c>
-      <c r="D2" t="s">
-        <v>35</v>
+      <c r="D2" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>1</v>
@@ -619,8 +730,8 @@
       <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2">
-        <v>289.25587023221198</v>
+      <c r="H2" s="5">
+        <v>289.2558702</v>
       </c>
       <c r="I2">
         <v>56.8238073528996</v>
@@ -632,21 +743,18 @@
         <v>46.8252349035102</v>
       </c>
       <c r="L2">
-        <v>379.46032512658797</v>
+        <v>19.031604767446499</v>
       </c>
       <c r="M2">
-        <v>19.031604767446499</v>
+        <v>5.2544176501106002E-2</v>
       </c>
       <c r="N2">
-        <v>5.2544176501106002E-2</v>
-      </c>
-      <c r="O2">
         <v>1.7443722912739299</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B3" s="1">
         <v>46247</v>
@@ -654,8 +762,8 @@
       <c r="C3" s="2">
         <v>0.68237268518518523</v>
       </c>
-      <c r="D3" t="s">
-        <v>35</v>
+      <c r="D3" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>1</v>
@@ -666,8 +774,8 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3">
-        <v>290.40810353633202</v>
+      <c r="H3" s="6">
+        <v>290.40810349999998</v>
       </c>
       <c r="I3">
         <v>65.197766604441</v>
@@ -678,22 +786,19 @@
       <c r="K3">
         <v>90.630564636909696</v>
       </c>
-      <c r="L3" s="3">
-        <v>-7.0148150136145E+28</v>
+      <c r="L3">
+        <v>0.40207699784454998</v>
       </c>
       <c r="M3">
-        <v>0.40207699784454998</v>
+        <v>2.48708582028017</v>
       </c>
       <c r="N3">
-        <v>2.48708582028017</v>
-      </c>
-      <c r="O3">
         <v>2.8963148766865601</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>22</v>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B4" s="1">
         <v>46247</v>
@@ -701,8 +806,8 @@
       <c r="C4" s="2">
         <v>0.68259259259259264</v>
       </c>
-      <c r="D4" t="s">
-        <v>36</v>
+      <c r="D4" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>1</v>
@@ -713,8 +818,8 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
-        <v>260.993407261801</v>
+      <c r="H4" s="5">
+        <v>260.9934073</v>
       </c>
       <c r="I4">
         <v>60.331909714106096</v>
@@ -726,21 +831,18 @@
         <v>61.724140696776701</v>
       </c>
       <c r="L4">
-        <v>577.045066866002</v>
+        <v>8.8834383589549795</v>
       </c>
       <c r="M4">
-        <v>8.8834383589549795</v>
+        <v>0.112569025594909</v>
       </c>
       <c r="N4">
-        <v>0.112569025594909</v>
-      </c>
-      <c r="O4">
         <v>1.01152929639307</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>22</v>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B5" s="1">
         <v>46247</v>
@@ -748,8 +850,8 @@
       <c r="C5" s="2">
         <v>0.68281250000000004</v>
       </c>
-      <c r="D5" t="s">
-        <v>36</v>
+      <c r="D5" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>1</v>
@@ -760,8 +862,8 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5">
-        <v>262.24952922801799</v>
+      <c r="H5" s="6">
+        <v>262.24952919999998</v>
       </c>
       <c r="I5">
         <v>65.985944547827799</v>
@@ -773,21 +875,18 @@
         <v>66.0060379203439</v>
       </c>
       <c r="L5">
-        <v>744.55886206709602</v>
+        <v>2.8030492326410501</v>
       </c>
       <c r="M5">
-        <v>2.8030492326410501</v>
+        <v>0.35675434749955998</v>
       </c>
       <c r="N5">
-        <v>0.35675434749955998</v>
-      </c>
-      <c r="O5">
         <v>2.4027916339091</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>23</v>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B6" s="1">
         <v>46247</v>
@@ -795,8 +894,8 @@
       <c r="C6" s="2">
         <v>0.68297453703703703</v>
       </c>
-      <c r="D6" t="s">
-        <v>35</v>
+      <c r="D6" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>1</v>
@@ -807,8 +906,8 @@
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="H6">
-        <v>321.837330640049</v>
+      <c r="H6" s="5">
+        <v>321.83733059999997</v>
       </c>
       <c r="I6">
         <v>65.921659933341999</v>
@@ -820,21 +919,18 @@
         <v>64.9788573204237</v>
       </c>
       <c r="L6">
-        <v>645.241845575855</v>
+        <v>16.4447934519382</v>
       </c>
       <c r="M6">
-        <v>16.4447934519382</v>
+        <v>6.0809520224295602E-2</v>
       </c>
       <c r="N6">
-        <v>6.0809520224295602E-2</v>
-      </c>
-      <c r="O6">
         <v>2.3154526692663802</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>23</v>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="B7" s="1">
         <v>46247</v>
@@ -842,8 +938,8 @@
       <c r="C7" s="2">
         <v>0.68343750000000003</v>
       </c>
-      <c r="D7" t="s">
-        <v>35</v>
+      <c r="D7" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="E7" t="s">
         <v>1</v>
@@ -854,8 +950,8 @@
       <c r="G7">
         <v>1</v>
       </c>
-      <c r="H7">
-        <v>307.359868774012</v>
+      <c r="H7" s="6">
+        <v>307.35986880000002</v>
       </c>
       <c r="I7">
         <v>68.084511251677299</v>
@@ -867,21 +963,18 @@
         <v>68.157781003404494</v>
       </c>
       <c r="L7">
-        <v>865.051899143073</v>
+        <v>3.7598318380487399</v>
       </c>
       <c r="M7">
-        <v>3.7598318380487399</v>
+        <v>0.26596934200093802</v>
       </c>
       <c r="N7">
-        <v>0.26596934200093802</v>
-      </c>
-      <c r="O7">
         <v>1.7413641013862899</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>23</v>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B8" s="1">
         <v>46247</v>
@@ -889,8 +982,8 @@
       <c r="C8" s="2">
         <v>0.68358796296296298</v>
       </c>
-      <c r="D8" t="s">
-        <v>36</v>
+      <c r="D8" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E8" t="s">
         <v>1</v>
@@ -901,8 +994,8 @@
       <c r="G8">
         <v>1</v>
       </c>
-      <c r="H8">
-        <v>302.49279743102301</v>
+      <c r="H8" s="5">
+        <v>302.49279739999997</v>
       </c>
       <c r="I8">
         <v>67.241000677082894</v>
@@ -914,21 +1007,18 @@
         <v>66.361098873016701</v>
       </c>
       <c r="L8">
-        <v>788.80450410320498</v>
+        <v>13.0156161221567</v>
       </c>
       <c r="M8">
-        <v>13.0156161221567</v>
+        <v>7.6830784698519394E-2</v>
       </c>
       <c r="N8">
-        <v>7.6830784698519394E-2</v>
-      </c>
-      <c r="O8">
         <v>2.6495852673522098</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>23</v>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="B9" s="1">
         <v>46247</v>
@@ -936,8 +1026,8 @@
       <c r="C9" s="2">
         <v>0.68385416666666665</v>
       </c>
-      <c r="D9" t="s">
-        <v>36</v>
+      <c r="D9" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="E9" t="s">
         <v>1</v>
@@ -948,8 +1038,8 @@
       <c r="G9">
         <v>1</v>
       </c>
-      <c r="H9">
-        <v>286.05810551962799</v>
+      <c r="H9" s="6">
+        <v>286.05810550000001</v>
       </c>
       <c r="I9">
         <v>55.014207020772901</v>
@@ -961,21 +1051,18 @@
         <v>54.5583903260884</v>
       </c>
       <c r="L9">
-        <v>852.28966472971297</v>
+        <v>3.0775724880036099</v>
       </c>
       <c r="M9">
-        <v>3.0775724880036099</v>
+        <v>0.32493142042892698</v>
       </c>
       <c r="N9">
-        <v>0.32493142042892698</v>
-      </c>
-      <c r="O9">
         <v>3.6702866925317998</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>24</v>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B10" s="1">
         <v>46247</v>
@@ -983,8 +1070,8 @@
       <c r="C10" s="2">
         <v>0.68450231481481483</v>
       </c>
-      <c r="D10" t="s">
-        <v>35</v>
+      <c r="D10" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="E10" t="s">
         <v>1</v>
@@ -995,8 +1082,8 @@
       <c r="G10">
         <v>1</v>
       </c>
-      <c r="H10">
-        <v>278.28849566886402</v>
+      <c r="H10" s="5">
+        <v>278.2884957</v>
       </c>
       <c r="I10">
         <v>76.265801414796798</v>
@@ -1008,21 +1095,18 @@
         <v>75.734708265207004</v>
       </c>
       <c r="L10">
-        <v>739.16569724590602</v>
+        <v>4.9810132911129497</v>
       </c>
       <c r="M10">
-        <v>4.9810132911129497</v>
+        <v>0.20076236330952699</v>
       </c>
       <c r="N10">
-        <v>0.20076236330952699</v>
-      </c>
-      <c r="O10">
         <v>2.5537610903161498</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>24</v>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B11" s="1">
         <v>46247</v>
@@ -1030,8 +1114,8 @@
       <c r="C11" s="2">
         <v>0.68484953703703699</v>
       </c>
-      <c r="D11" t="s">
-        <v>35</v>
+      <c r="D11" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="E11" t="s">
         <v>1</v>
@@ -1042,8 +1126,8 @@
       <c r="G11">
         <v>1</v>
       </c>
-      <c r="H11">
-        <v>281.97597406809001</v>
+      <c r="H11" s="6">
+        <v>281.97597409999997</v>
       </c>
       <c r="I11">
         <v>57.5394058372557</v>
@@ -1055,21 +1139,18 @@
         <v>61.386682749189198</v>
       </c>
       <c r="L11">
-        <v>1114.67283008355</v>
+        <v>3.5517267559504999</v>
       </c>
       <c r="M11">
-        <v>3.5517267559504999</v>
+        <v>0.281553190521939</v>
       </c>
       <c r="N11">
-        <v>0.281553190521939</v>
-      </c>
-      <c r="O11">
         <v>1.86264933935785</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>24</v>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B12" s="1">
         <v>46247</v>
@@ -1077,8 +1158,8 @@
       <c r="C12" s="2">
         <v>0.6849884259259259</v>
       </c>
-      <c r="D12" t="s">
-        <v>36</v>
+      <c r="D12" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E12" t="s">
         <v>1</v>
@@ -1089,8 +1170,8 @@
       <c r="G12">
         <v>1</v>
       </c>
-      <c r="H12">
-        <v>296.87740248569497</v>
+      <c r="H12" s="5">
+        <v>296.87740250000002</v>
       </c>
       <c r="I12">
         <v>67.229042311017494</v>
@@ -1102,20 +1183,17 @@
         <v>69.171422135308305</v>
       </c>
       <c r="L12">
-        <v>1238.4008602367901</v>
+        <v>3.3818642449511498</v>
       </c>
       <c r="M12">
-        <v>3.3818642449511498</v>
+        <v>0.295694897124543</v>
       </c>
       <c r="N12">
-        <v>0.295694897124543</v>
-      </c>
-      <c r="O12">
         <v>2.0669878871324099</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="1">
@@ -1124,8 +1202,8 @@
       <c r="C13" s="2">
         <v>0.68520833333333331</v>
       </c>
-      <c r="D13" t="s">
-        <v>36</v>
+      <c r="D13" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="E13" t="s">
         <v>1</v>
@@ -1136,8 +1214,8 @@
       <c r="G13">
         <v>1</v>
       </c>
-      <c r="H13">
-        <v>330.38177598207199</v>
+      <c r="H13" s="6">
+        <v>330.381776</v>
       </c>
       <c r="I13">
         <v>63.540302184683902</v>
@@ -1149,20 +1227,17 @@
         <v>63.460538661638303</v>
       </c>
       <c r="L13">
-        <v>930.87873010261796</v>
+        <v>7.2949455925108202</v>
       </c>
       <c r="M13">
-        <v>7.2949455925108202</v>
+        <v>0.13708121428988099</v>
       </c>
       <c r="N13">
-        <v>0.13708121428988099</v>
-      </c>
-      <c r="O13">
         <v>1.4639823117572699</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B14" s="1">
@@ -1171,8 +1246,8 @@
       <c r="C14" s="2">
         <v>0.68539351851851849</v>
       </c>
-      <c r="D14" t="s">
-        <v>35</v>
+      <c r="D14" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="E14" t="s">
         <v>1</v>
@@ -1183,8 +1258,8 @@
       <c r="G14">
         <v>1</v>
       </c>
-      <c r="H14">
-        <v>338.71496479507402</v>
+      <c r="H14" s="5">
+        <v>338.71496480000002</v>
       </c>
       <c r="I14">
         <v>73.615156731600393</v>
@@ -1196,21 +1271,18 @@
         <v>75.952750582142997</v>
       </c>
       <c r="L14">
-        <v>455.21541467512401</v>
+        <v>6.3819790512722498</v>
       </c>
       <c r="M14">
-        <v>6.3819790512722498</v>
+        <v>0.15669120690715099</v>
       </c>
       <c r="N14">
-        <v>0.15669120690715099</v>
-      </c>
-      <c r="O14">
         <v>2.4182622728324299</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>22</v>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B15" s="1">
         <v>46247</v>
@@ -1218,7 +1290,7 @@
       <c r="C15" s="2">
         <v>0.6856944444444445</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E15" t="s">
@@ -1230,8 +1302,8 @@
       <c r="G15">
         <v>1</v>
       </c>
-      <c r="H15">
-        <v>206.73610310663901</v>
+      <c r="H15" s="6">
+        <v>206.73610310000001</v>
       </c>
       <c r="I15">
         <v>70.940194222800898</v>
@@ -1243,21 +1315,18 @@
         <v>70.426907536767203</v>
       </c>
       <c r="L15">
-        <v>772.90812356524896</v>
+        <v>8.5392578584853105</v>
       </c>
       <c r="M15">
-        <v>8.5392578584853105</v>
+        <v>0.117106195476498</v>
       </c>
       <c r="N15">
-        <v>0.117106195476498</v>
-      </c>
-      <c r="O15">
         <v>1.4042950200892399</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>22</v>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B16" s="1">
         <v>46247</v>
@@ -1265,7 +1334,7 @@
       <c r="C16" s="2">
         <v>0.68593749999999998</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E16" t="s">
@@ -1277,8 +1346,8 @@
       <c r="G16">
         <v>1</v>
       </c>
-      <c r="H16">
-        <v>193.68219721689499</v>
+      <c r="H16" s="5">
+        <v>193.68219719999999</v>
       </c>
       <c r="I16">
         <v>69.888547283056397</v>
@@ -1290,21 +1359,18 @@
         <v>70.355426881363201</v>
       </c>
       <c r="L16">
-        <v>538.04199927288596</v>
+        <v>5.2061826747129798</v>
       </c>
       <c r="M16">
-        <v>5.2061826747129798</v>
+        <v>0.19207931463048999</v>
       </c>
       <c r="N16">
-        <v>0.19207931463048999</v>
-      </c>
-      <c r="O16">
         <v>2.1963621574269898</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>22</v>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B17" s="1">
         <v>46247</v>
@@ -1312,7 +1378,7 @@
       <c r="C17" s="2">
         <v>0.68667824074074069</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E17" t="s">
@@ -1324,8 +1390,8 @@
       <c r="G17">
         <v>1</v>
       </c>
-      <c r="H17">
-        <v>220.32948135573301</v>
+      <c r="H17" s="6">
+        <v>220.32948139999999</v>
       </c>
       <c r="I17">
         <v>86.625756465048795</v>
@@ -1337,21 +1403,18 @@
         <v>86.583650618796597</v>
       </c>
       <c r="L17">
-        <v>897.44655761257695</v>
+        <v>11.0700610338037</v>
       </c>
       <c r="M17">
-        <v>11.0700610338037</v>
+        <v>9.0333738625865606E-2</v>
       </c>
       <c r="N17">
-        <v>9.0333738625865606E-2</v>
-      </c>
-      <c r="O17">
         <v>3.2612875156453298</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>22</v>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B18" s="1">
         <v>46247</v>
@@ -1359,7 +1422,7 @@
       <c r="C18" s="2">
         <v>0.68687500000000001</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E18" t="s">
@@ -1371,8 +1434,8 @@
       <c r="G18">
         <v>1</v>
       </c>
-      <c r="H18">
-        <v>155.19411535616899</v>
+      <c r="H18" s="5">
+        <v>155.19411539999999</v>
       </c>
       <c r="I18">
         <v>87.590397481714803</v>
@@ -1384,21 +1447,18 @@
         <v>99.711657525245101</v>
       </c>
       <c r="L18">
-        <v>684.79660843400598</v>
+        <v>7.2872070278993304</v>
       </c>
       <c r="M18">
-        <v>7.2872070278993304</v>
+        <v>0.13722678608847899</v>
       </c>
       <c r="N18">
-        <v>0.13722678608847899</v>
-      </c>
-      <c r="O18">
         <v>2.3100247922362298</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>23</v>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="B19" s="1">
         <v>46247</v>
@@ -1406,7 +1466,7 @@
       <c r="C19" s="2">
         <v>0.68706018518518519</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E19" t="s">
@@ -1418,8 +1478,8 @@
       <c r="G19">
         <v>1</v>
       </c>
-      <c r="H19">
-        <v>269.20193140466603</v>
+      <c r="H19" s="6">
+        <v>269.20193139999998</v>
       </c>
       <c r="I19">
         <v>68.660759127430893</v>
@@ -1431,21 +1491,18 @@
         <v>68.168738777279898</v>
       </c>
       <c r="L19">
-        <v>251.55676846441901</v>
+        <v>3.82437806246715</v>
       </c>
       <c r="M19">
-        <v>3.82437806246715</v>
+        <v>0.261480424703328</v>
       </c>
       <c r="N19">
-        <v>0.261480424703328</v>
-      </c>
-      <c r="O19">
         <v>5.3921932813620304</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>23</v>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B20" s="1">
         <v>46247</v>
@@ -1453,7 +1510,7 @@
       <c r="C20" s="2">
         <v>0.68723379629629633</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E20" t="s">
@@ -1465,8 +1522,8 @@
       <c r="G20">
         <v>1</v>
       </c>
-      <c r="H20">
-        <v>255.10218791135401</v>
+      <c r="H20" s="5">
+        <v>255.10218789999999</v>
       </c>
       <c r="I20">
         <v>81.395664078762195</v>
@@ -1478,21 +1535,18 @@
         <v>81.220052709267804</v>
       </c>
       <c r="L20">
-        <v>955.44222176287997</v>
+        <v>10.675733922780401</v>
       </c>
       <c r="M20">
-        <v>10.675733922780401</v>
+        <v>9.3670375004958797E-2</v>
       </c>
       <c r="N20">
-        <v>9.3670375004958797E-2</v>
-      </c>
-      <c r="O20">
         <v>1.24599704747739</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>23</v>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="B21" s="1">
         <v>46247</v>
@@ -1500,7 +1554,7 @@
       <c r="C21" s="2">
         <v>0.68739583333333332</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E21" t="s">
@@ -1512,8 +1566,8 @@
       <c r="G21">
         <v>1</v>
       </c>
-      <c r="H21">
-        <v>276.181541763849</v>
+      <c r="H21" s="6">
+        <v>276.18154179999999</v>
       </c>
       <c r="I21">
         <v>71.521568172164294</v>
@@ -1525,21 +1579,18 @@
         <v>70.940185281625006</v>
       </c>
       <c r="L21">
-        <v>935.443266057286</v>
+        <v>11.6782652623472</v>
       </c>
       <c r="M21">
-        <v>11.6782652623472</v>
+        <v>8.5629156174776497E-2</v>
       </c>
       <c r="N21">
-        <v>8.5629156174776497E-2</v>
-      </c>
-      <c r="O21">
         <v>2.4311324656625399</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>23</v>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B22" s="1">
         <v>46247</v>
@@ -1547,7 +1598,7 @@
       <c r="C22" s="2">
         <v>0.68761574074074072</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E22" t="s">
@@ -1559,8 +1610,8 @@
       <c r="G22">
         <v>1</v>
       </c>
-      <c r="H22">
-        <v>262.20863472877602</v>
+      <c r="H22" s="5">
+        <v>262.2086347</v>
       </c>
       <c r="I22">
         <v>78.960967592186705</v>
@@ -1572,21 +1623,18 @@
         <v>83.013978613382903</v>
       </c>
       <c r="L22">
-        <v>652.50809054022295</v>
+        <v>1.93222966107956</v>
       </c>
       <c r="M22">
-        <v>1.93222966107956</v>
+        <v>0.51753682294747805</v>
       </c>
       <c r="N22">
-        <v>0.51753682294747805</v>
-      </c>
-      <c r="O22">
         <v>1.6522700274525299</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>24</v>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B23" s="1">
         <v>46247</v>
@@ -1594,7 +1642,7 @@
       <c r="C23" s="2">
         <v>0.68783564814814813</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E23" t="s">
@@ -1606,8 +1654,8 @@
       <c r="G23">
         <v>1</v>
       </c>
-      <c r="H23">
-        <v>183.477642835138</v>
+      <c r="H23" s="6">
+        <v>183.47764280000001</v>
       </c>
       <c r="I23">
         <v>72.970428641746807</v>
@@ -1619,21 +1667,18 @@
         <v>73.1627981602755</v>
       </c>
       <c r="L23">
-        <v>548.21551265805203</v>
+        <v>4.11394755029142</v>
       </c>
       <c r="M23">
-        <v>4.11394755029142</v>
+        <v>0.24307553457485401</v>
       </c>
       <c r="N23">
-        <v>0.24307553457485401</v>
-      </c>
-      <c r="O23">
         <v>1.7004598905289501</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>24</v>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B24" s="1">
         <v>46247</v>
@@ -1641,7 +1686,7 @@
       <c r="C24" s="2">
         <v>0.6880208333333333</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E24" t="s">
@@ -1653,8 +1698,8 @@
       <c r="G24">
         <v>1</v>
       </c>
-      <c r="H24">
-        <v>175.86876396265001</v>
+      <c r="H24" s="5">
+        <v>175.868764</v>
       </c>
       <c r="I24">
         <v>75.642473587838893</v>
@@ -1666,21 +1711,18 @@
         <v>73.754567256993099</v>
       </c>
       <c r="L24">
-        <v>190.96028010655201</v>
+        <v>4.42592876614719</v>
       </c>
       <c r="M24">
-        <v>4.42592876614719</v>
+        <v>0.225941277602285</v>
       </c>
       <c r="N24">
-        <v>0.225941277602285</v>
-      </c>
-      <c r="O24">
         <v>3.4026037055172602</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>24</v>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B25" s="1">
         <v>46247</v>
@@ -1688,7 +1730,7 @@
       <c r="C25" s="2">
         <v>0.66896990740740736</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E25" t="s">
@@ -1700,8 +1742,8 @@
       <c r="G25">
         <v>1</v>
       </c>
-      <c r="H25">
-        <v>169.17884302337299</v>
+      <c r="H25" s="6">
+        <v>169.178843</v>
       </c>
       <c r="I25">
         <v>56.8238073528996</v>
@@ -1712,19 +1754,19 @@
       <c r="K25">
         <v>46.8252349035102</v>
       </c>
+      <c r="L25">
+        <v>19.031604767446499</v>
+      </c>
       <c r="M25">
-        <v>19.031604767446499</v>
+        <v>5.2544176501106002E-2</v>
       </c>
       <c r="N25">
-        <v>5.2544176501106002E-2</v>
-      </c>
-      <c r="O25">
         <v>1.7443722912739299</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>24</v>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B26" s="1">
         <v>46247</v>
@@ -1732,7 +1774,7 @@
       <c r="C26" s="2">
         <v>0.68237268518518523</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E26" t="s">
@@ -1744,8 +1786,8 @@
       <c r="G26">
         <v>1</v>
       </c>
-      <c r="H26">
-        <v>172.27100469440299</v>
+      <c r="H26" s="5">
+        <v>172.27100469999999</v>
       </c>
       <c r="I26">
         <v>65.197766604441</v>
@@ -1757,20 +1799,17 @@
         <v>90.630564636909696</v>
       </c>
       <c r="L26">
-        <v>167.36611891939401</v>
+        <v>0.40207699784454998</v>
       </c>
       <c r="M26">
-        <v>0.40207699784454998</v>
+        <v>2.48708582028017</v>
       </c>
       <c r="N26">
-        <v>2.48708582028017</v>
-      </c>
-      <c r="O26">
         <v>2.8963148766865601</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B27" s="1">
@@ -1779,7 +1818,7 @@
       <c r="C27" s="2">
         <v>0.68259259259259264</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E27" t="s">
@@ -1791,8 +1830,8 @@
       <c r="G27">
         <v>1</v>
       </c>
-      <c r="H27">
-        <v>253.662325685898</v>
+      <c r="H27" s="6">
+        <v>253.6623257</v>
       </c>
       <c r="I27">
         <v>60.331909714106096</v>
@@ -1804,20 +1843,17 @@
         <v>61.724140696776701</v>
       </c>
       <c r="L27">
-        <v>944.58178356615394</v>
+        <v>8.8834383589549795</v>
       </c>
       <c r="M27">
-        <v>8.8834383589549795</v>
+        <v>0.112569025594909</v>
       </c>
       <c r="N27">
-        <v>0.112569025594909</v>
-      </c>
-      <c r="O27">
         <v>1.01152929639307</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B28" s="1">
@@ -1826,7 +1862,7 @@
       <c r="C28" s="2">
         <v>0.68281250000000004</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E28" t="s">
@@ -1838,8 +1874,8 @@
       <c r="G28">
         <v>1</v>
       </c>
-      <c r="H28">
-        <v>181.990770138578</v>
+      <c r="H28" s="5">
+        <v>181.99077009999999</v>
       </c>
       <c r="I28">
         <v>65.985944547827799</v>
@@ -1851,20 +1887,17 @@
         <v>66.0060379203439</v>
       </c>
       <c r="L28">
-        <v>693.555629759775</v>
+        <v>2.8030492326410501</v>
       </c>
       <c r="M28">
-        <v>2.8030492326410501</v>
+        <v>0.35675434749955998</v>
       </c>
       <c r="N28">
-        <v>0.35675434749955998</v>
-      </c>
-      <c r="O28">
         <v>2.4027916339091</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="1">
@@ -1873,7 +1906,7 @@
       <c r="C29" s="2">
         <v>0.68297453703703703</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D29" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E29" t="s">
@@ -1885,8 +1918,8 @@
       <c r="G29">
         <v>1</v>
       </c>
-      <c r="H29">
-        <v>305.44775512179302</v>
+      <c r="H29" s="6">
+        <v>305.44775509999999</v>
       </c>
       <c r="I29">
         <v>65.921659933341999</v>
@@ -1898,20 +1931,17 @@
         <v>64.9788573204237</v>
       </c>
       <c r="L29">
-        <v>500.90380502457498</v>
+        <v>16.4447934519382</v>
       </c>
       <c r="M29">
-        <v>16.4447934519382</v>
+        <v>6.0809520224295602E-2</v>
       </c>
       <c r="N29">
-        <v>6.0809520224295602E-2</v>
-      </c>
-      <c r="O29">
         <v>2.3154526692663802</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B30" s="1">
@@ -1920,7 +1950,7 @@
       <c r="C30" s="2">
         <v>0.68343750000000003</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E30" t="s">
@@ -1932,8 +1962,8 @@
       <c r="G30">
         <v>1</v>
       </c>
-      <c r="H30">
-        <v>77.099259002155193</v>
+      <c r="H30" s="5">
+        <v>77.099259000000004</v>
       </c>
       <c r="I30">
         <v>68.084511251677299</v>
@@ -1944,19 +1974,19 @@
       <c r="K30">
         <v>68.157781003404494</v>
       </c>
+      <c r="L30">
+        <v>3.7598318380487399</v>
+      </c>
       <c r="M30">
-        <v>3.7598318380487399</v>
+        <v>0.26596934200093802</v>
       </c>
       <c r="N30">
-        <v>0.26596934200093802</v>
-      </c>
-      <c r="O30">
         <v>1.7413641013862899</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>22</v>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="B31" s="1">
         <v>46247</v>
@@ -1964,8 +1994,8 @@
       <c r="C31" s="2">
         <v>0.68358796296296298</v>
       </c>
-      <c r="D31" t="s">
-        <v>37</v>
+      <c r="D31" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="E31" t="s">
         <v>1</v>
@@ -1976,8 +2006,8 @@
       <c r="G31">
         <v>1</v>
       </c>
-      <c r="H31">
-        <v>452.61610194763301</v>
+      <c r="H31" s="6">
+        <v>452.61610189999999</v>
       </c>
       <c r="I31">
         <v>67.241000677082894</v>
@@ -1989,21 +2019,18 @@
         <v>66.361098873016701</v>
       </c>
       <c r="L31">
-        <v>712.76072516122804</v>
+        <v>13.0156161221567</v>
       </c>
       <c r="M31">
-        <v>13.0156161221567</v>
+        <v>7.6830784698519394E-2</v>
       </c>
       <c r="N31">
-        <v>7.6830784698519394E-2</v>
-      </c>
-      <c r="O31">
         <v>2.6495852673522098</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>22</v>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>21</v>
       </c>
       <c r="B32" s="1">
         <v>46247</v>
@@ -2011,8 +2038,8 @@
       <c r="C32" s="2">
         <v>0.68385416666666665</v>
       </c>
-      <c r="D32" t="s">
-        <v>38</v>
+      <c r="D32" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="E32" t="s">
         <v>1</v>
@@ -2023,8 +2050,8 @@
       <c r="G32">
         <v>1</v>
       </c>
-      <c r="H32">
-        <v>437.87886237248102</v>
+      <c r="H32" s="5">
+        <v>437.8788624</v>
       </c>
       <c r="I32">
         <v>55.014207020772901</v>
@@ -2036,21 +2063,18 @@
         <v>54.5583903260884</v>
       </c>
       <c r="L32">
-        <v>874.68049400842904</v>
+        <v>3.0775724880036099</v>
       </c>
       <c r="M32">
-        <v>3.0775724880036099</v>
+        <v>0.32493142042892698</v>
       </c>
       <c r="N32">
-        <v>0.32493142042892698</v>
-      </c>
-      <c r="O32">
         <v>3.6702866925317998</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>23</v>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="B33" s="1">
         <v>46247</v>
@@ -2058,8 +2082,8 @@
       <c r="C33" s="2">
         <v>0.68450231481481483</v>
       </c>
-      <c r="D33" t="s">
-        <v>37</v>
+      <c r="D33" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="E33" t="s">
         <v>1</v>
@@ -2070,8 +2094,8 @@
       <c r="G33">
         <v>1</v>
       </c>
-      <c r="H33">
-        <v>516.34935110781396</v>
+      <c r="H33" s="6">
+        <v>516.34935110000004</v>
       </c>
       <c r="I33">
         <v>76.265801414796798</v>
@@ -2083,21 +2107,18 @@
         <v>75.734708265207004</v>
       </c>
       <c r="L33">
-        <v>1090.06330871809</v>
+        <v>4.9810132911129497</v>
       </c>
       <c r="M33">
-        <v>4.9810132911129497</v>
+        <v>0.20076236330952699</v>
       </c>
       <c r="N33">
-        <v>0.20076236330952699</v>
-      </c>
-      <c r="O33">
         <v>2.5537610903161498</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>23</v>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="B34" s="1">
         <v>46247</v>
@@ -2105,8 +2126,8 @@
       <c r="C34" s="2">
         <v>0.68484953703703699</v>
       </c>
-      <c r="D34" t="s">
-        <v>38</v>
+      <c r="D34" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="E34" t="s">
         <v>1</v>
@@ -2117,8 +2138,8 @@
       <c r="G34">
         <v>1</v>
       </c>
-      <c r="H34">
-        <v>541.07073811590794</v>
+      <c r="H34" s="5">
+        <v>541.07073809999997</v>
       </c>
       <c r="I34">
         <v>57.5394058372557</v>
@@ -2130,21 +2151,18 @@
         <v>61.386682749189198</v>
       </c>
       <c r="L34">
-        <v>1093.7015305636501</v>
+        <v>3.5517267559504999</v>
       </c>
       <c r="M34">
-        <v>3.5517267559504999</v>
+        <v>0.281553190521939</v>
       </c>
       <c r="N34">
-        <v>0.281553190521939</v>
-      </c>
-      <c r="O34">
         <v>1.86264933935785</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>24</v>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="B35" s="1">
         <v>46247</v>
@@ -2152,8 +2170,8 @@
       <c r="C35" s="2">
         <v>0.6849884259259259</v>
       </c>
-      <c r="D35" t="s">
-        <v>37</v>
+      <c r="D35" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="E35" t="s">
         <v>1</v>
@@ -2164,8 +2182,8 @@
       <c r="G35">
         <v>1</v>
       </c>
-      <c r="H35">
-        <v>354.99597997651301</v>
+      <c r="H35" s="6">
+        <v>354.99597999999997</v>
       </c>
       <c r="I35">
         <v>67.229042311017494</v>
@@ -2177,21 +2195,18 @@
         <v>69.171422135308305</v>
       </c>
       <c r="L35">
-        <v>1189.4756031808199</v>
+        <v>3.3818642449511498</v>
       </c>
       <c r="M35">
-        <v>3.3818642449511498</v>
+        <v>0.295694897124543</v>
       </c>
       <c r="N35">
-        <v>0.295694897124543</v>
-      </c>
-      <c r="O35">
         <v>2.0669878871324099</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>24</v>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="B36" s="1">
         <v>46247</v>
@@ -2199,8 +2214,8 @@
       <c r="C36" s="2">
         <v>0.68520833333333331</v>
       </c>
-      <c r="D36" t="s">
-        <v>38</v>
+      <c r="D36" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="E36" t="s">
         <v>1</v>
@@ -2211,8 +2226,8 @@
       <c r="G36">
         <v>1</v>
       </c>
-      <c r="H36">
-        <v>456.246040300733</v>
+      <c r="H36" s="5">
+        <v>456.2460403</v>
       </c>
       <c r="I36">
         <v>63.540302184683902</v>
@@ -2224,20 +2239,17 @@
         <v>63.460538661638303</v>
       </c>
       <c r="L36">
-        <v>1466.3363982073499</v>
+        <v>7.2949455925108202</v>
       </c>
       <c r="M36">
-        <v>7.2949455925108202</v>
+        <v>0.13708121428988099</v>
       </c>
       <c r="N36">
-        <v>0.13708121428988099</v>
-      </c>
-      <c r="O36">
         <v>1.4639823117572699</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B37" s="1">
@@ -2246,8 +2258,8 @@
       <c r="C37" s="2">
         <v>0.68539351851851849</v>
       </c>
-      <c r="D37" t="s">
-        <v>37</v>
+      <c r="D37" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="E37" t="s">
         <v>1</v>
@@ -2258,8 +2270,8 @@
       <c r="G37">
         <v>1</v>
       </c>
-      <c r="H37">
-        <v>540.99161873109301</v>
+      <c r="H37" s="6">
+        <v>540.9916187</v>
       </c>
       <c r="I37">
         <v>73.615156731600393</v>
@@ -2271,20 +2283,17 @@
         <v>75.952750582142997</v>
       </c>
       <c r="L37">
-        <v>1284.2555750802501</v>
+        <v>6.3819790512722498</v>
       </c>
       <c r="M37">
-        <v>6.3819790512722498</v>
+        <v>0.15669120690715099</v>
       </c>
       <c r="N37">
-        <v>0.15669120690715099</v>
-      </c>
-      <c r="O37">
         <v>2.4182622728324299</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B38" s="1">
@@ -2293,8 +2302,8 @@
       <c r="C38" s="2">
         <v>0.6856944444444445</v>
       </c>
-      <c r="D38" t="s">
-        <v>38</v>
+      <c r="D38" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="E38" t="s">
         <v>1</v>
@@ -2305,8 +2314,8 @@
       <c r="G38">
         <v>1</v>
       </c>
-      <c r="H38">
-        <v>589.24878634687002</v>
+      <c r="H38" s="5">
+        <v>589.24878630000001</v>
       </c>
       <c r="I38">
         <v>70.940194222800898</v>
@@ -2318,21 +2327,18 @@
         <v>70.426907536767203</v>
       </c>
       <c r="L38">
-        <v>1169.8698332127601</v>
+        <v>8.5392578584853105</v>
       </c>
       <c r="M38">
-        <v>8.5392578584853105</v>
+        <v>0.117106195476498</v>
       </c>
       <c r="N38">
-        <v>0.117106195476498</v>
-      </c>
-      <c r="O38">
         <v>1.4042950200892399</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>25</v>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B39" s="1">
         <v>46247</v>
@@ -2340,8 +2346,8 @@
       <c r="C39" s="2">
         <v>0.68593749999999998</v>
       </c>
-      <c r="D39" t="s">
-        <v>35</v>
+      <c r="D39" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="E39" t="s">
         <v>1</v>
@@ -2352,8 +2358,8 @@
       <c r="G39">
         <v>1</v>
       </c>
-      <c r="H39">
-        <v>194.32365381184499</v>
+      <c r="H39" s="6">
+        <v>194.32365379999999</v>
       </c>
       <c r="I39">
         <v>69.888547283056397</v>
@@ -2365,21 +2371,18 @@
         <v>70.355426881363201</v>
       </c>
       <c r="L39">
-        <v>1252.28793795447</v>
+        <v>5.2061826747129798</v>
       </c>
       <c r="M39">
-        <v>5.2061826747129798</v>
+        <v>0.19207931463048999</v>
       </c>
       <c r="N39">
-        <v>0.19207931463048999</v>
-      </c>
-      <c r="O39">
         <v>2.1963621574269898</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>25</v>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B40" s="1">
         <v>46247</v>
@@ -2387,8 +2390,8 @@
       <c r="C40" s="2">
         <v>0.68667824074074069</v>
       </c>
-      <c r="D40" t="s">
-        <v>36</v>
+      <c r="D40" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E40" t="s">
         <v>1</v>
@@ -2399,8 +2402,8 @@
       <c r="G40">
         <v>1</v>
       </c>
-      <c r="H40">
-        <v>284.64919674340001</v>
+      <c r="H40" s="5">
+        <v>284.6491967</v>
       </c>
       <c r="I40">
         <v>86.625756465048795</v>
@@ -2412,21 +2415,18 @@
         <v>86.583650618796597</v>
       </c>
       <c r="L40">
-        <v>693.44873977700695</v>
+        <v>11.0700610338037</v>
       </c>
       <c r="M40">
-        <v>11.0700610338037</v>
+        <v>9.0333738625865606E-2</v>
       </c>
       <c r="N40">
-        <v>9.0333738625865606E-2</v>
-      </c>
-      <c r="O40">
         <v>3.2612875156453298</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>25</v>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B41" s="1">
         <v>46247</v>
@@ -2434,7 +2434,7 @@
       <c r="C41" s="2">
         <v>0.68687500000000001</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E41" t="s">
@@ -2446,8 +2446,8 @@
       <c r="G41">
         <v>1</v>
       </c>
-      <c r="H41">
-        <v>158.77410557019601</v>
+      <c r="H41" s="6">
+        <v>158.77410560000001</v>
       </c>
       <c r="I41">
         <v>87.590397481714803</v>
@@ -2458,19 +2458,19 @@
       <c r="K41">
         <v>99.711657525245101</v>
       </c>
+      <c r="L41">
+        <v>7.2872070278993304</v>
+      </c>
       <c r="M41">
-        <v>7.2872070278993304</v>
+        <v>0.13722678608847899</v>
       </c>
       <c r="N41">
-        <v>0.13722678608847899</v>
-      </c>
-      <c r="O41">
         <v>2.3100247922362298</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>25</v>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B42" s="1">
         <v>46247</v>
@@ -2478,7 +2478,7 @@
       <c r="C42" s="2">
         <v>0.68706018518518519</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E42" t="s">
@@ -2490,8 +2490,8 @@
       <c r="G42">
         <v>1</v>
       </c>
-      <c r="H42">
-        <v>199.796437973835</v>
+      <c r="H42" s="5">
+        <v>199.79643799999999</v>
       </c>
       <c r="I42">
         <v>68.660759127430893</v>
@@ -2503,21 +2503,18 @@
         <v>68.168738777279898</v>
       </c>
       <c r="L42">
-        <v>1290.8932313727501</v>
+        <v>3.82437806246715</v>
       </c>
       <c r="M42">
-        <v>3.82437806246715</v>
+        <v>0.261480424703328</v>
       </c>
       <c r="N42">
-        <v>0.261480424703328</v>
-      </c>
-      <c r="O42">
         <v>5.3921932813620304</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>25</v>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="B43" s="1">
         <v>46247</v>
@@ -2525,7 +2522,7 @@
       <c r="C43" s="2">
         <v>0.68723379629629633</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E43" t="s">
@@ -2537,8 +2534,8 @@
       <c r="G43">
         <v>1</v>
       </c>
-      <c r="H43">
-        <v>161.82188748652399</v>
+      <c r="H43" s="6">
+        <v>161.8218875</v>
       </c>
       <c r="I43">
         <v>81.395664078762195</v>
@@ -2550,21 +2547,18 @@
         <v>81.220052709267804</v>
       </c>
       <c r="L43">
-        <v>1118.7506591245201</v>
+        <v>10.675733922780401</v>
       </c>
       <c r="M43">
-        <v>10.675733922780401</v>
+        <v>9.3670375004958797E-2</v>
       </c>
       <c r="N43">
-        <v>9.3670375004958797E-2</v>
-      </c>
-      <c r="O43">
         <v>1.24599704747739</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>25</v>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B44" s="1">
         <v>46247</v>
@@ -2572,7 +2566,7 @@
       <c r="C44" s="2">
         <v>0.68739583333333332</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="5" t="s">
         <v>5</v>
       </c>
       <c r="E44" t="s">
@@ -2584,8 +2578,8 @@
       <c r="G44">
         <v>1</v>
       </c>
-      <c r="H44">
-        <v>178.76463249610001</v>
+      <c r="H44" s="5">
+        <v>178.7646325</v>
       </c>
       <c r="I44">
         <v>71.521568172164294</v>
@@ -2597,21 +2591,18 @@
         <v>70.940185281625006</v>
       </c>
       <c r="L44">
-        <v>1242.25360723616</v>
+        <v>11.6782652623472</v>
       </c>
       <c r="M44">
-        <v>11.6782652623472</v>
+        <v>8.5629156174776497E-2</v>
       </c>
       <c r="N44">
-        <v>8.5629156174776497E-2</v>
-      </c>
-      <c r="O44">
         <v>2.4311324656625399</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>26</v>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="B45" s="1">
         <v>46247</v>
@@ -2619,8 +2610,8 @@
       <c r="C45" s="2">
         <v>0.68761574074074072</v>
       </c>
-      <c r="D45" t="s">
-        <v>35</v>
+      <c r="D45" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="E45" t="s">
         <v>1</v>
@@ -2631,8 +2622,8 @@
       <c r="G45">
         <v>1</v>
       </c>
-      <c r="H45">
-        <v>180.79037691030399</v>
+      <c r="H45" s="6">
+        <v>180.79037690000001</v>
       </c>
       <c r="I45">
         <v>78.960967592186705</v>
@@ -2644,21 +2635,18 @@
         <v>83.013978613382903</v>
       </c>
       <c r="L45">
-        <v>739.29483630878599</v>
+        <v>1.93222966107956</v>
       </c>
       <c r="M45">
-        <v>1.93222966107956</v>
+        <v>0.51753682294747805</v>
       </c>
       <c r="N45">
-        <v>0.51753682294747805</v>
-      </c>
-      <c r="O45">
         <v>1.6522700274525299</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>26</v>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="B46" s="1">
         <v>46247</v>
@@ -2666,8 +2654,8 @@
       <c r="C46" s="2">
         <v>0.68783564814814813</v>
       </c>
-      <c r="D46" t="s">
-        <v>36</v>
+      <c r="D46" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E46" t="s">
         <v>1</v>
@@ -2678,8 +2666,8 @@
       <c r="G46">
         <v>1</v>
       </c>
-      <c r="H46">
-        <v>236.07431460472699</v>
+      <c r="H46" s="5">
+        <v>236.07431460000001</v>
       </c>
       <c r="I46">
         <v>72.970428641746807</v>
@@ -2691,21 +2679,18 @@
         <v>73.1627981602755</v>
       </c>
       <c r="L46">
-        <v>507.94850896611501</v>
+        <v>4.11394755029142</v>
       </c>
       <c r="M46">
-        <v>4.11394755029142</v>
+        <v>0.24307553457485401</v>
       </c>
       <c r="N46">
-        <v>0.24307553457485401</v>
-      </c>
-      <c r="O46">
         <v>1.7004598905289501</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>26</v>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="B47" s="1">
         <v>46247</v>
@@ -2713,7 +2698,7 @@
       <c r="C47" s="2">
         <v>0.6880208333333333</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E47" t="s">
@@ -2725,8 +2710,8 @@
       <c r="G47">
         <v>1</v>
       </c>
-      <c r="H47">
-        <v>205.414238166654</v>
+      <c r="H47" s="6">
+        <v>205.4142382</v>
       </c>
       <c r="I47">
         <v>75.642473587838893</v>
@@ -2738,1303 +2723,2523 @@
         <v>73.754567256993099</v>
       </c>
       <c r="L47">
-        <v>1137.80370939927</v>
+        <v>4.42592876614719</v>
       </c>
       <c r="M47">
-        <v>4.42592876614719</v>
+        <v>0.225941277602285</v>
       </c>
       <c r="N47">
-        <v>0.225941277602285</v>
-      </c>
-      <c r="O47">
         <v>3.4026037055172602</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="5">
+        <v>144.37411979999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H49" s="6">
+        <v>193.43378530000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50" s="5">
+        <v>176.32150559999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B48" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" t="s">
+      <c r="B51" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" s="6">
+        <v>135.8206696</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H52" s="5">
+        <v>203.67206039999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H53" s="6">
+        <v>255.8223328</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H48">
-        <v>144.37411977902599</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
+      <c r="H54" s="5">
+        <v>194.4636156</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B49" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" t="s">
+      <c r="B55" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H49">
-        <v>193.43378534266699</v>
-      </c>
-      <c r="L49">
-        <v>188.42571810457201</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
+      <c r="H55" s="6">
+        <v>186.24094009999999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s">
+      <c r="B56" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H50">
-        <v>176.321505645765</v>
-      </c>
-      <c r="L50">
-        <v>1070.88170097181</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
+      <c r="H56" s="5">
+        <v>206.31038849999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H57" s="6">
+        <v>285.39934890000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H58" s="5">
+        <v>254.25659619999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H59" s="6">
+        <v>487.70941199999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H60" s="5">
+        <v>574.48955279999996</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H61" s="6">
+        <v>186.7757569</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H62" s="5">
+        <v>185.4482118</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B51" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s">
+      <c r="B63" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" s="6">
+        <v>323.89606270000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="H51">
-        <v>135.82066962637401</v>
-      </c>
-      <c r="L51">
-        <v>746.60173289408101</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
+      <c r="H64" s="5">
+        <v>343.0741453</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B52" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C52" s="2"/>
-      <c r="D52" t="s">
+      <c r="B65" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H65" s="6">
+        <v>154.34435049999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="5">
+        <v>221.89954800000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H67" s="6">
+        <v>167.04643139999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68" s="5">
+        <v>213.9536622</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H69" s="6">
+        <v>168.87268460000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H70" s="5">
+        <v>140.4895769</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H71" s="6">
+        <v>127.426401</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="5">
+        <v>139.79164650000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H73" s="6">
+        <v>135.39181020000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H74" s="5">
+        <v>91.754979019999993</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H52">
-        <v>203.67206036466101</v>
-      </c>
-      <c r="L52">
-        <v>336.40634358601397</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
+      <c r="H75" s="6">
+        <v>207.50756860000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H76" s="5">
+        <v>275.95332139999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H77" s="6">
+        <v>259.52012150000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H78" s="5">
+        <v>174.30199379999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H79" s="6">
+        <v>198.18359409999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H80" s="5">
+        <v>240.35464020000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B53" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C53" s="2"/>
-      <c r="D53" t="s">
+      <c r="B81" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H81" s="6">
+        <v>391.77702349999998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H82" s="5">
+        <v>234.74759359999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H83" s="6">
+        <v>248.0546329</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H84" s="5">
+        <v>533.34955500000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H85" s="6">
+        <v>358.6193705</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B86" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H86" s="5">
+        <v>294.44187770000002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B87" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H87" s="6">
+        <v>348.02439950000002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H88" s="5">
+        <v>289.41865080000002</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H89" s="6">
+        <v>394.62818720000001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H90" s="5">
+        <v>495.1236672</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B91" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H91" s="6">
+        <v>638.05849409999996</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H92" s="5">
+        <v>369.07202769999998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H93" s="6">
+        <v>137.06804149999999</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H94" s="5">
+        <v>243.46135290000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H95" s="6">
+        <v>162.58819560000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H96" s="5">
+        <v>172.63177490000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H97" s="6">
+        <v>197.61111679999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H98" s="5">
+        <v>199.668813</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H99" s="6">
+        <v>166.2743327</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H100" s="5">
+        <v>266.04587759999998</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B101" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H101" s="6">
+        <v>93.533578230000003</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B102" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H102" s="5">
+        <v>136.4429877</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B103" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H53">
-        <v>255.82233283162901</v>
-      </c>
-      <c r="L53">
-        <v>1332.45217041909</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>27</v>
-      </c>
-      <c r="B54" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s">
+      <c r="H103" s="6">
+        <v>150.5110401</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H54">
-        <v>194.463615565032</v>
-      </c>
-      <c r="L54">
-        <v>1346.9112306105301</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>27</v>
-      </c>
-      <c r="B55" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s">
+      <c r="H104" s="5">
+        <v>114.458748</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B105" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H55">
-        <v>186.24094010229399</v>
-      </c>
-      <c r="L55">
-        <v>765.13706484240402</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>27</v>
-      </c>
-      <c r="B56" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s">
+      <c r="H105" s="6">
+        <v>185.3021664</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B106" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H56">
-        <v>206.31038845646799</v>
-      </c>
-      <c r="L56">
-        <v>1271.32539016743</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>25</v>
-      </c>
-      <c r="B57" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s">
+      <c r="H106" s="5">
+        <v>119.5918262</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B107" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H107" s="6">
+        <v>224.68302120000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B108" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H108" s="5">
+        <v>194.46670460000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B109" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H109" s="6">
+        <v>209.1531013</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B110" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H110" s="5">
+        <v>172.13383730000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H111" s="6">
+        <v>167.2321278</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B112" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H112" s="5">
+        <v>129.54443219999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B113" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H113" s="6">
+        <v>151.15603719999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H114" s="5">
+        <v>147.72051099999999</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H115" s="6">
+        <v>152.7670392</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H116" s="5">
+        <v>141.9040335</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B117" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H117" s="6">
+        <v>121.2997744</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B118" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H118" s="5">
+        <v>121.8374331</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B119" s="1">
+        <v>46247</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H119" s="6">
+        <v>150.29659599999999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B120" s="1"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H120" s="5">
+        <v>180.06260829999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B121" s="1"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H121" s="6">
+        <v>225.93275460000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B122" s="1"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H122" s="5">
+        <v>144.84907369999999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B123" s="1"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H123" s="6">
+        <v>133.95486880000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B124" s="1"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H124" s="5">
+        <v>156.69124980000001</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B125" s="1"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H125" s="6">
+        <v>148.8782918</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B126" s="1"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H126" s="5">
+        <v>205.73288149999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B127" s="1"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H127" s="6">
+        <v>201.42807640000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B128" s="1"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H128" s="5">
+        <v>216.98947949999999</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B129" s="1"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H129" s="6">
+        <v>180.54462229999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A130" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B130" s="1"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H130" s="5">
+        <v>250.58714710000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B131" s="1"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H131" s="6">
+        <v>165.69648910000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B132" s="1"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H132" s="5">
+        <v>236.35815579999999</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B133" s="1"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H133" s="6">
+        <v>222.43647089999999</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B134" s="1"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H134" s="5">
+        <v>220.46097639999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B135" s="1"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H135" s="6">
+        <v>203.63844370000001</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B136" s="1"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H136" s="5">
+        <v>246.56549849999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A137" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B137" s="1"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H137" s="6">
+        <v>182.15375370000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A138" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B138" s="1"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H138" s="5">
+        <v>295.72373399999998</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A139" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B139" s="1"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H57">
-        <v>285.399348863066</v>
-      </c>
-      <c r="L57">
-        <v>1214.7445873828599</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>25</v>
-      </c>
-      <c r="B58" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s">
-        <v>38</v>
-      </c>
-      <c r="H58">
-        <v>254.25659617779701</v>
-      </c>
-      <c r="L58">
-        <v>1335.80610380843</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>26</v>
-      </c>
-      <c r="B59" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s">
+      <c r="H139" s="6">
+        <v>337.66075039999998</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A140" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B140" s="1"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H140" s="5">
+        <v>522.91274439999995</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A141" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B141" s="1"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H59">
-        <v>487.70941201555001</v>
-      </c>
-      <c r="L59">
-        <v>1347.5335731294899</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>26</v>
-      </c>
-      <c r="B60" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s">
-        <v>38</v>
-      </c>
-      <c r="H60">
-        <v>574.48955280392602</v>
-      </c>
-      <c r="L60">
-        <v>2405.4168622206898</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>27</v>
-      </c>
-      <c r="B61" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s">
+      <c r="H141" s="6">
+        <v>495.28936629999998</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A142" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B142" s="1"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H142" s="5">
+        <v>276.9300159</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A143" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B143" s="1"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H61">
-        <v>186.775756871423</v>
-      </c>
-      <c r="L61">
-        <v>836.54920600734704</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s">
-        <v>38</v>
-      </c>
-      <c r="H62">
-        <v>185.44821179498001</v>
-      </c>
-      <c r="L62">
-        <v>755.08235736881704</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>28</v>
-      </c>
-      <c r="B63" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s">
+      <c r="H143" s="6">
+        <v>372.58477749999997</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A144" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B144" s="1"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H144" s="5">
+        <v>236.2484164</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B145" s="1"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H63">
-        <v>323.89606271525798</v>
-      </c>
-      <c r="L63">
-        <v>1101.85415436877</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>28</v>
-      </c>
-      <c r="B64" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s">
+      <c r="H145" s="6">
+        <v>186.313479</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A146" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B146" s="1"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H146" s="5">
+        <v>161.06850030000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B147" s="1"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H147" s="6">
+        <v>171.29538529999999</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B148" s="1"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H148" s="5">
+        <v>137.90134610000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A149" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B149" s="1"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H149" s="6">
+        <v>204.5812517</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B150" s="1"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H150" s="5">
+        <v>218.8364828</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A151" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B151" s="1"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H151" s="6">
+        <v>113.8385181</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B152" s="1"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H152" s="5">
+        <v>178.9581096</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B153" s="1"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H153" s="6">
+        <v>171.2764975</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A154" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B154" s="1"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H154" s="5">
+        <v>200.281181</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B155" s="1"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H155" s="6">
+        <v>221.35168859999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B156" s="1"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H156" s="5">
+        <v>259.92938650000002</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B157" s="1"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H157" s="6">
+        <v>243.79377099999999</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A158" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B158" s="1"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H158" s="5">
+        <v>218.97287320000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A159" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B159" s="1"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H159" s="6">
+        <v>264.32066730000003</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H64">
-        <v>343.074145341041</v>
-      </c>
-      <c r="L64">
-        <v>1156.7315372191099</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>28</v>
-      </c>
-      <c r="B65" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s">
+      <c r="H160" s="5">
+        <v>438.7023231</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B161" s="1"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H161" s="6">
+        <v>379.40431919999997</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A162" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B162" s="1"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H162" s="5">
+        <v>376.33962630000002</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B163" s="1"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H163" s="6">
+        <v>339.18861049999998</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A164" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B164" s="1"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H164" s="5">
+        <v>640.09017819999997</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B165" s="1"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H165" s="6">
+        <v>480.28347380000002</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A166" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B166" s="1"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H166" s="5">
+        <v>262.12501049999997</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B167" s="1"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H167" s="6">
+        <v>269.35283900000002</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A168" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B168" s="1"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H65">
-        <v>154.344350536641</v>
-      </c>
-      <c r="L65">
-        <v>1036.0907179804301</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>28</v>
-      </c>
-      <c r="B66" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s">
+      <c r="H168" s="5">
+        <v>227.6929883</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B169" s="1"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H66">
-        <v>221.899547954925</v>
-      </c>
-      <c r="L66">
-        <v>1039.9921642826801</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>28</v>
-      </c>
-      <c r="B67" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s">
+      <c r="H169" s="6">
+        <v>213.7080192</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A170" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B170" s="1"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H67">
-        <v>167.04643137153599</v>
-      </c>
-      <c r="L67">
-        <v>1045.3357573005901</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>28</v>
-      </c>
-      <c r="B68" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s">
+      <c r="H170" s="5">
+        <v>194.50148830000001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B171" s="1"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H68">
-        <v>213.95366223602301</v>
-      </c>
-      <c r="L68">
-        <v>947.68789759652805</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>29</v>
-      </c>
-      <c r="B69" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s">
+      <c r="H171" s="6">
+        <v>211.0257263</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A172" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B172" s="1"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H172" s="5">
+        <v>130.20692679999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B173" s="1"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H69">
-        <v>168.87268460100699</v>
-      </c>
-      <c r="L69">
-        <v>18.0022053657184</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>29</v>
-      </c>
-      <c r="B70" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="D70" t="s">
+      <c r="H173" s="6">
+        <v>154.3101637</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A174" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B174" s="1"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H174" s="5">
+        <v>143.3240644</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B175" s="1"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H175" s="6">
+        <v>142.73418580000001</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B176" s="1"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H176" s="5">
+        <v>179.48385709999999</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B177" s="1"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H177" s="6">
+        <v>145.2943306</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A178" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B178" s="1"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H70">
-        <v>140.48957688096999</v>
-      </c>
-      <c r="L70">
-        <v>526.68558465019998</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>29</v>
-      </c>
-      <c r="B71" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C71" s="2"/>
-      <c r="D71" t="s">
+      <c r="H178" s="5">
+        <v>203.10090400000001</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B179" s="1"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H179" s="6">
+        <v>231.3776508</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A180" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B180" s="1"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H180" s="5">
+        <v>212.47936139999999</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B181" s="1"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H181" s="6">
+        <v>206.96393380000001</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A182" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B182" s="1"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H71">
-        <v>127.42640102186201</v>
-      </c>
-      <c r="L71">
-        <v>597.17029269262105</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>29</v>
-      </c>
-      <c r="B72" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s">
+      <c r="H182" s="5">
+        <v>248.84443920000001</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B183" s="1"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H72">
-        <v>139.791646502916</v>
-      </c>
-      <c r="L72">
-        <v>748.05326371848003</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>29</v>
-      </c>
-      <c r="B73" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s">
+      <c r="H183" s="6">
+        <v>247.54656499999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A184" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B184" s="1"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H184" s="5">
+        <v>195.67129610000001</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B185" s="1"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H185" s="6">
+        <v>188.0125453</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A186" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B186" s="1"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H73">
-        <v>135.39181024553</v>
-      </c>
-      <c r="L73">
-        <v>784.34952174150601</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>29</v>
-      </c>
-      <c r="B74" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s">
+      <c r="H186" s="5">
+        <v>175.4859491</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B187" s="1"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H74">
-        <v>91.754979017412396</v>
-      </c>
-      <c r="L74">
-        <v>462.63081258683098</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>29</v>
-      </c>
-      <c r="B75" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s">
+      <c r="H187" s="6">
+        <v>160.39012750000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A188" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B188" s="1"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H188" s="5">
+        <v>159.1863506</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B189" s="1"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H189" s="6">
+        <v>135.8546585</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B190" s="1"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H75">
-        <v>207.50756856236299</v>
-      </c>
-      <c r="L75">
-        <v>315.21634585677401</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>29</v>
-      </c>
-      <c r="B76" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s">
-        <v>38</v>
-      </c>
-      <c r="H76">
-        <v>275.95332144227302</v>
-      </c>
-      <c r="L76">
-        <v>597.332609627686</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s">
+      <c r="H190" s="5">
+        <v>438.3048976</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B191" s="1"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H191" s="6">
+        <v>606.19166459999997</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B192" s="1"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H192" s="5">
+        <v>372.71017460000002</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B193" s="1"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H193" s="6">
+        <v>347.98340760000002</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B194" s="1"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H194" s="5">
+        <v>651.06983390000005</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B195" s="1"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H195" s="6">
+        <v>423.51136129999998</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B196" s="1"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H196" s="5">
+        <v>271.73044490000001</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B197" s="1"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H197" s="6">
+        <v>351.83396090000002</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B198" s="1"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H198" s="5">
+        <v>183.56903790000001</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B199" s="1"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H199" s="6">
+        <v>184.0172914</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B200" s="1"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H200" s="5">
+        <v>139.66764620000001</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B201" s="1"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H77">
-        <v>259.52012147360699</v>
-      </c>
-      <c r="L77">
-        <v>892.92983544509298</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>30</v>
-      </c>
-      <c r="B78" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s">
+      <c r="H201" s="6">
+        <v>131.4923541</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B202" s="1"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H202" s="5">
+        <v>149.52161319999999</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B203" s="1"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H203" s="6">
+        <v>131.02269939999999</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A204" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B204" s="1"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H204" s="5">
+        <v>227.23962929999999</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B205" s="1"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H205" s="6">
+        <v>227.9269773</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A206" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B206" s="1"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H206" s="5">
+        <v>216.18608080000001</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B207" s="1"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H207" s="6">
+        <v>140.8273495</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B208" s="1"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H208" s="5">
+        <v>193.9871292</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B209" s="1"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H78">
-        <v>174.301993760285</v>
-      </c>
-      <c r="L78">
-        <v>1198.5885708216299</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s">
+      <c r="H209" s="6">
+        <v>141.35643469999999</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B210" s="1"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H210" s="5">
+        <v>236.75833349999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B211" s="1"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H211" s="6">
+        <v>263.56862719999998</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B212" s="1"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H212" s="5">
+        <v>271.24947850000001</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B213" s="1"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H213" s="6">
+        <v>192.74452819999999</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B214" s="1"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H214" s="5">
+        <v>239.46257309999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A215" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B215" s="1"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H79">
-        <v>198.183594144555</v>
-      </c>
-      <c r="L79">
-        <v>1332.4061302279299</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>30</v>
-      </c>
-      <c r="B80" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s">
+      <c r="H215" s="6">
+        <v>164.13982559999999</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A216" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B216" s="1"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H216" s="5">
+        <v>195.5292068</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A217" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B217" s="1"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H217" s="6">
+        <v>179.66785719999999</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A218" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B218" s="1"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H218" s="5">
+        <v>178.1463938</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B219" s="1"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H219" s="6">
+        <v>151.06453780000001</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A220" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B220" s="1"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="H80">
-        <v>240.35464024935899</v>
-      </c>
-      <c r="L80">
-        <v>1146.6979485320201</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>28</v>
-      </c>
-      <c r="B81" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s">
+      <c r="H220" s="5">
+        <v>169.51222519999999</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A221" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B221" s="1"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H221" s="6">
+        <v>156.43160549999999</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A222" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B222" s="1"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H222" s="5">
+        <v>384.39131099999997</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A223" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B223" s="1"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H81">
-        <v>391.77702352852998</v>
-      </c>
-      <c r="L81">
-        <v>880.01344198444701</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>30</v>
-      </c>
-      <c r="B82" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s">
-        <v>35</v>
-      </c>
-      <c r="H82">
-        <v>234.74759355253599</v>
-      </c>
-      <c r="L82">
-        <v>1415.4735006865899</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>30</v>
-      </c>
-      <c r="B83" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s">
+      <c r="H223" s="6">
+        <v>374.53152899999998</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A224" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B224" s="1"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H83">
-        <v>248.05463289630299</v>
-      </c>
-      <c r="L83">
-        <v>1647.9369562182001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>28</v>
-      </c>
-      <c r="B84" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s">
-        <v>38</v>
-      </c>
-      <c r="H84">
-        <v>533.34955497838598</v>
-      </c>
-      <c r="L84" s="3">
-        <v>-1.01930822864721E+30</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>30</v>
-      </c>
-      <c r="B85" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s">
+      <c r="H224" s="5">
+        <v>258.39252909999999</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A225" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B225" s="1"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H85">
-        <v>358.61937049900598</v>
-      </c>
-      <c r="L85">
-        <v>900.291177480584</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>30</v>
-      </c>
-      <c r="B86" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s">
-        <v>38</v>
-      </c>
-      <c r="H86">
-        <v>294.44187771783299</v>
-      </c>
-      <c r="L86">
-        <v>1684.5291541822701</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>31</v>
-      </c>
-      <c r="B87" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s">
-        <v>38</v>
-      </c>
-      <c r="H87">
-        <v>348.02439952114599</v>
-      </c>
-      <c r="L87">
-        <v>541.65076606346804</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>31</v>
-      </c>
-      <c r="B88" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s">
+      <c r="H225" s="6">
+        <v>262.27258410000002</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B226" s="1"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H88">
-        <v>289.418650785789</v>
-      </c>
-      <c r="L88">
-        <v>348.37986024774301</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>32</v>
-      </c>
-      <c r="B89" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s">
+      <c r="H226" s="5">
+        <v>610.31778589999999</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A227" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B227" s="1"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H227" s="6">
+        <v>756.06069579999996</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A228" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B228" s="1"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H228" s="5">
+        <v>396.74451349999998</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A229" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B229" s="1"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="H89">
-        <v>394.62818721071102</v>
-      </c>
-      <c r="L89">
-        <v>2565.2096550433898</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>32</v>
-      </c>
-      <c r="B90" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s">
-        <v>38</v>
-      </c>
-      <c r="H90">
-        <v>495.12366719147798</v>
-      </c>
-      <c r="L90">
-        <v>1919.8058948543301</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>33</v>
-      </c>
-      <c r="B91" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s">
-        <v>38</v>
-      </c>
-      <c r="H91">
-        <v>638.05849410390204</v>
-      </c>
-      <c r="L91">
-        <v>1276.3123983437499</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>33</v>
-      </c>
-      <c r="B92" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s">
-        <v>37</v>
-      </c>
-      <c r="H92">
-        <v>369.07202765014398</v>
-      </c>
-      <c r="L92">
-        <v>1637.7622036288899</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>34</v>
-      </c>
-      <c r="B93" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s">
-        <v>38</v>
-      </c>
-      <c r="H93">
-        <v>137.068041477619</v>
-      </c>
-      <c r="L93">
-        <v>464.25480152752601</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>34</v>
-      </c>
-      <c r="B94" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s">
-        <v>37</v>
-      </c>
-      <c r="H94">
-        <v>243.46135286167899</v>
-      </c>
-      <c r="L94">
-        <v>320.26247018007899</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>31</v>
-      </c>
-      <c r="B95" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s">
-        <v>36</v>
-      </c>
-      <c r="H95">
-        <v>162.58819555391</v>
-      </c>
-      <c r="L95">
-        <v>959.37470863552005</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>31</v>
-      </c>
-      <c r="B96" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s">
-        <v>35</v>
-      </c>
-      <c r="H96">
-        <v>172.63177491649699</v>
-      </c>
-      <c r="L96">
-        <v>864.00344262149201</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>32</v>
-      </c>
-      <c r="B97" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s">
-        <v>36</v>
-      </c>
-      <c r="H97">
-        <v>197.611116773492</v>
-      </c>
-      <c r="L97">
-        <v>1175.25050819066</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>32</v>
-      </c>
-      <c r="B98" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s">
-        <v>35</v>
-      </c>
-      <c r="H98">
-        <v>199.668812967251</v>
-      </c>
-      <c r="L98">
-        <v>1336.71834206021</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>33</v>
-      </c>
-      <c r="B99" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s">
-        <v>35</v>
-      </c>
-      <c r="H99">
-        <v>166.27433274294299</v>
-      </c>
-      <c r="L99">
-        <v>918.992476753593</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>33</v>
-      </c>
-      <c r="B100" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s">
-        <v>36</v>
-      </c>
-      <c r="H100">
-        <v>266.04587760875199</v>
-      </c>
-      <c r="L100">
-        <v>250.73044563827699</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>34</v>
-      </c>
-      <c r="B101" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s">
-        <v>35</v>
-      </c>
-      <c r="H101">
-        <v>93.533578225030098</v>
-      </c>
-      <c r="L101">
-        <v>222.732204039501</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>34</v>
-      </c>
-      <c r="B102" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s">
-        <v>36</v>
-      </c>
-      <c r="H102">
-        <v>136.44298772302699</v>
-      </c>
-      <c r="L102">
-        <v>127.63819815730599</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>31</v>
-      </c>
-      <c r="B103" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s">
-        <v>3</v>
-      </c>
-      <c r="H103">
-        <v>150.51104005821199</v>
-      </c>
-      <c r="L103">
-        <v>987.90428201393695</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>31</v>
-      </c>
-      <c r="B104" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s">
-        <v>5</v>
-      </c>
-      <c r="H104">
-        <v>114.45874801253601</v>
-      </c>
-      <c r="L104">
-        <v>670.40597859371201</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>31</v>
-      </c>
-      <c r="B105" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s">
-        <v>2</v>
-      </c>
-      <c r="H105">
-        <v>185.30216638166999</v>
-      </c>
-      <c r="L105">
-        <v>925.36525777901704</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>31</v>
-      </c>
-      <c r="B106" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s">
-        <v>4</v>
-      </c>
-      <c r="H106">
-        <v>119.59182620434299</v>
-      </c>
-      <c r="L106">
-        <v>443.09740034904303</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>32</v>
-      </c>
-      <c r="B107" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s">
-        <v>3</v>
-      </c>
-      <c r="H107">
-        <v>224.68302121025701</v>
-      </c>
-      <c r="L107">
-        <v>1207.3492977439701</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>32</v>
-      </c>
-      <c r="B108" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s">
-        <v>5</v>
-      </c>
-      <c r="H108">
-        <v>194.466704596288</v>
-      </c>
-      <c r="L108">
-        <v>1272.57277576974</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>32</v>
-      </c>
-      <c r="B109" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s">
-        <v>2</v>
-      </c>
-      <c r="H109">
-        <v>209.153101333287</v>
-      </c>
-      <c r="L109">
-        <v>1217.59296523392</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>32</v>
-      </c>
-      <c r="B110" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s">
-        <v>4</v>
-      </c>
-      <c r="H110">
-        <v>172.13383734504501</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>33</v>
-      </c>
-      <c r="B111" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s">
-        <v>3</v>
-      </c>
-      <c r="H111">
-        <v>167.23212784208599</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>33</v>
-      </c>
-      <c r="B112" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s">
-        <v>3</v>
-      </c>
-      <c r="H112">
-        <v>129.544432205063</v>
-      </c>
-      <c r="L112">
-        <v>422.922647919886</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>33</v>
-      </c>
-      <c r="B113" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s">
-        <v>5</v>
-      </c>
-      <c r="H113">
-        <v>151.15603715980399</v>
-      </c>
-      <c r="L113">
-        <v>706.84626676823405</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>33</v>
-      </c>
-      <c r="B114" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s">
-        <v>2</v>
-      </c>
-      <c r="H114">
-        <v>147.72051099000001</v>
-      </c>
-      <c r="L114">
-        <v>57.578708711607298</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>33</v>
-      </c>
-      <c r="B115" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s">
-        <v>4</v>
-      </c>
-      <c r="H115">
-        <v>152.76703922515699</v>
-      </c>
-      <c r="L115">
-        <v>532.19822373433601</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>34</v>
-      </c>
-      <c r="B116" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s">
-        <v>3</v>
-      </c>
-      <c r="H116">
-        <v>141.90403350396801</v>
-      </c>
-      <c r="L116">
-        <v>661.02793295996298</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>34</v>
-      </c>
-      <c r="B117" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s">
-        <v>4</v>
-      </c>
-      <c r="H117">
-        <v>121.29977436612999</v>
-      </c>
-      <c r="L117">
-        <v>113.65274010442</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>34</v>
-      </c>
-      <c r="B118" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s">
-        <v>2</v>
-      </c>
-      <c r="H118">
-        <v>121.83743308515299</v>
-      </c>
-      <c r="L118">
-        <v>390.13215870333801</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>34</v>
-      </c>
-      <c r="B119" s="1">
-        <v>46247</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s">
-        <v>5</v>
-      </c>
-      <c r="H119">
-        <v>150.296595967196</v>
-      </c>
-      <c r="L119">
-        <v>453.872127357061</v>
+      <c r="H229" s="6">
+        <v>366.27056010000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/EVALUACIONES/FUERZA ANALITICA/DINAMOMETRIA_ANALITICO.xlsx
+++ b/data/EVALUACIONES/FUERZA ANALITICA/DINAMOMETRIA_ANALITICO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\EVALUACIONES\FUERZA ANALITICA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0C60DA-5A79-45A8-B04A-688C90FBEA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26C36DA-4C4E-4A11-8BF0-9EF98B904402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
+    <workbookView xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="9960" xr2:uid="{BBC13A56-B43E-4445-9420-3EF783FE99BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -288,6 +288,12 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color theme="4" tint="0.39997558519241921"/>
@@ -302,12 +308,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="26" formatCode="h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -326,9 +326,9 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}" name="Tabla1" displayName="Tabla1" ref="A1:O229" totalsRowShown="0">
   <autoFilter ref="A1:O229" xr:uid="{76854E88-9049-4297-B0F3-CF73409EEE8F}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{D8BDFCD4-5CB3-4377-9AAC-B345BFF21CCD}" name="Name" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{74190477-3FDA-4A91-AAD5-93B0F998FA90}" name="Date" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{EF7C01B4-3DD3-436A-AA24-BB5B8FE55AA0}" name="Time" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{D8BDFCD4-5CB3-4377-9AAC-B345BFF21CCD}" name="Name" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{74190477-3FDA-4A91-AAD5-93B0F998FA90}" name="Date" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{EF7C01B4-3DD3-436A-AA24-BB5B8FE55AA0}" name="Time" dataDxfId="2"/>
     <tableColumn id="4" xr3:uid="{EDD40885-F2D2-4308-AED6-F4BAAE7E61A8}" name="Exercise" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{6F0E5AF9-E656-486A-ABBA-C00C3BE0F5C9}" name="Laterality"/>
     <tableColumn id="6" xr3:uid="{913730D9-54FF-46DC-A12C-BDCBE0564973}" name="Set"/>
@@ -3816,7 +3816,9 @@
       <c r="A120" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B120" s="1"/>
+      <c r="B120" s="1">
+        <v>46247</v>
+      </c>
       <c r="C120" s="2"/>
       <c r="D120" s="5" t="s">
         <v>34</v>
@@ -3829,7 +3831,9 @@
       <c r="A121" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B121" s="1"/>
+      <c r="B121" s="1">
+        <v>46247</v>
+      </c>
       <c r="C121" s="2"/>
       <c r="D121" s="6" t="s">
         <v>35</v>
@@ -3842,7 +3846,9 @@
       <c r="A122" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B122" s="1"/>
+      <c r="B122" s="1">
+        <v>46247</v>
+      </c>
       <c r="C122" s="2"/>
       <c r="D122" s="5" t="s">
         <v>3</v>
@@ -3855,7 +3861,9 @@
       <c r="A123" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B123" s="1"/>
+      <c r="B123" s="1">
+        <v>46247</v>
+      </c>
       <c r="C123" s="2"/>
       <c r="D123" s="6" t="s">
         <v>5</v>
@@ -3868,7 +3876,9 @@
       <c r="A124" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B124" s="1"/>
+      <c r="B124" s="1">
+        <v>46247</v>
+      </c>
       <c r="C124" s="2"/>
       <c r="D124" s="5" t="s">
         <v>2</v>
@@ -3881,7 +3891,9 @@
       <c r="A125" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B125" s="1"/>
+      <c r="B125" s="1">
+        <v>46247</v>
+      </c>
       <c r="C125" s="2"/>
       <c r="D125" s="6" t="s">
         <v>4</v>
@@ -3894,7 +3906,9 @@
       <c r="A126" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B126" s="1"/>
+      <c r="B126" s="1">
+        <v>46247</v>
+      </c>
       <c r="C126" s="2"/>
       <c r="D126" s="5" t="s">
         <v>34</v>
@@ -3907,7 +3921,9 @@
       <c r="A127" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B127" s="1"/>
+      <c r="B127" s="1">
+        <v>46247</v>
+      </c>
       <c r="C127" s="2"/>
       <c r="D127" s="6" t="s">
         <v>35</v>
@@ -3920,7 +3936,9 @@
       <c r="A128" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B128" s="1"/>
+      <c r="B128" s="1">
+        <v>46247</v>
+      </c>
       <c r="C128" s="2"/>
       <c r="D128" s="5" t="s">
         <v>2</v>
@@ -3933,7 +3951,9 @@
       <c r="A129" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B129" s="1"/>
+      <c r="B129" s="1">
+        <v>46247</v>
+      </c>
       <c r="C129" s="2"/>
       <c r="D129" s="6" t="s">
         <v>4</v>
@@ -3946,7 +3966,9 @@
       <c r="A130" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B130" s="1"/>
+      <c r="B130" s="1">
+        <v>46247</v>
+      </c>
       <c r="C130" s="2"/>
       <c r="D130" s="5" t="s">
         <v>3</v>
@@ -3959,7 +3981,9 @@
       <c r="A131" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B131" s="1"/>
+      <c r="B131" s="1">
+        <v>46247</v>
+      </c>
       <c r="C131" s="2"/>
       <c r="D131" s="6" t="s">
         <v>5</v>
@@ -3972,7 +3996,9 @@
       <c r="A132" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B132" s="1"/>
+      <c r="B132" s="1">
+        <v>46247</v>
+      </c>
       <c r="C132" s="2"/>
       <c r="D132" s="5" t="s">
         <v>34</v>
@@ -3985,7 +4011,9 @@
       <c r="A133" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B133" s="1"/>
+      <c r="B133" s="1">
+        <v>46247</v>
+      </c>
       <c r="C133" s="2"/>
       <c r="D133" s="6" t="s">
         <v>35</v>
@@ -3998,7 +4026,9 @@
       <c r="A134" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B134" s="1"/>
+      <c r="B134" s="1">
+        <v>46247</v>
+      </c>
       <c r="C134" s="2"/>
       <c r="D134" s="5" t="s">
         <v>3</v>
@@ -4011,7 +4041,9 @@
       <c r="A135" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B135" s="1"/>
+      <c r="B135" s="1">
+        <v>46247</v>
+      </c>
       <c r="C135" s="2"/>
       <c r="D135" s="6" t="s">
         <v>5</v>
@@ -4024,7 +4056,9 @@
       <c r="A136" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B136" s="1"/>
+      <c r="B136" s="1">
+        <v>46247</v>
+      </c>
       <c r="C136" s="2"/>
       <c r="D136" s="5" t="s">
         <v>2</v>
@@ -4037,7 +4071,9 @@
       <c r="A137" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B137" s="1"/>
+      <c r="B137" s="1">
+        <v>46247</v>
+      </c>
       <c r="C137" s="2"/>
       <c r="D137" s="6" t="s">
         <v>4</v>
@@ -4050,7 +4086,9 @@
       <c r="A138" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B138" s="1"/>
+      <c r="B138" s="1">
+        <v>46247</v>
+      </c>
       <c r="C138" s="2"/>
       <c r="D138" s="5" t="s">
         <v>36</v>
@@ -4063,7 +4101,9 @@
       <c r="A139" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B139" s="1"/>
+      <c r="B139" s="1">
+        <v>46247</v>
+      </c>
       <c r="C139" s="2"/>
       <c r="D139" s="6" t="s">
         <v>37</v>
@@ -4076,7 +4116,9 @@
       <c r="A140" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B140" s="1"/>
+      <c r="B140" s="1">
+        <v>46247</v>
+      </c>
       <c r="C140" s="2"/>
       <c r="D140" s="5" t="s">
         <v>36</v>
@@ -4089,7 +4131,9 @@
       <c r="A141" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B141" s="1"/>
+      <c r="B141" s="1">
+        <v>46247</v>
+      </c>
       <c r="C141" s="2"/>
       <c r="D141" s="6" t="s">
         <v>37</v>
@@ -4102,7 +4146,9 @@
       <c r="A142" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B142" s="1"/>
+      <c r="B142" s="1">
+        <v>46247</v>
+      </c>
       <c r="C142" s="2"/>
       <c r="D142" s="5" t="s">
         <v>36</v>
@@ -4115,7 +4161,9 @@
       <c r="A143" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B143" s="1"/>
+      <c r="B143" s="1">
+        <v>46247</v>
+      </c>
       <c r="C143" s="2"/>
       <c r="D143" s="6" t="s">
         <v>37</v>
@@ -4128,7 +4176,9 @@
       <c r="A144" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B144" s="1"/>
+      <c r="B144" s="1">
+        <v>46247</v>
+      </c>
       <c r="C144" s="2"/>
       <c r="D144" s="5" t="s">
         <v>34</v>
@@ -4141,7 +4191,9 @@
       <c r="A145" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B145" s="1"/>
+      <c r="B145" s="1">
+        <v>46247</v>
+      </c>
       <c r="C145" s="2"/>
       <c r="D145" s="6" t="s">
         <v>35</v>
@@ -4154,7 +4206,9 @@
       <c r="A146" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B146" s="1"/>
+      <c r="B146" s="1">
+        <v>46247</v>
+      </c>
       <c r="C146" s="2"/>
       <c r="D146" s="5" t="s">
         <v>3</v>
@@ -4167,7 +4221,9 @@
       <c r="A147" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B147" s="1"/>
+      <c r="B147" s="1">
+        <v>46247</v>
+      </c>
       <c r="C147" s="2"/>
       <c r="D147" s="6" t="s">
         <v>5</v>
@@ -4180,7 +4236,9 @@
       <c r="A148" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B148" s="1"/>
+      <c r="B148" s="1">
+        <v>46247</v>
+      </c>
       <c r="C148" s="2"/>
       <c r="D148" s="5" t="s">
         <v>4</v>
@@ -4193,7 +4251,9 @@
       <c r="A149" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B149" s="1"/>
+      <c r="B149" s="1">
+        <v>46247</v>
+      </c>
       <c r="C149" s="2"/>
       <c r="D149" s="6" t="s">
         <v>2</v>
@@ -4206,7 +4266,9 @@
       <c r="A150" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B150" s="1"/>
+      <c r="B150" s="1">
+        <v>46247</v>
+      </c>
       <c r="C150" s="2"/>
       <c r="D150" s="5" t="s">
         <v>34</v>
@@ -4219,7 +4281,9 @@
       <c r="A151" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B151" s="1"/>
+      <c r="B151" s="1">
+        <v>46247</v>
+      </c>
       <c r="C151" s="2"/>
       <c r="D151" s="6" t="s">
         <v>35</v>
@@ -4232,7 +4296,9 @@
       <c r="A152" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B152" s="1"/>
+      <c r="B152" s="1">
+        <v>46247</v>
+      </c>
       <c r="C152" s="2"/>
       <c r="D152" s="5" t="s">
         <v>2</v>
@@ -4245,7 +4311,9 @@
       <c r="A153" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B153" s="1"/>
+      <c r="B153" s="1">
+        <v>46247</v>
+      </c>
       <c r="C153" s="2"/>
       <c r="D153" s="6" t="s">
         <v>4</v>
@@ -4258,7 +4326,9 @@
       <c r="A154" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B154" s="1"/>
+      <c r="B154" s="1">
+        <v>46247</v>
+      </c>
       <c r="C154" s="2"/>
       <c r="D154" s="5" t="s">
         <v>5</v>
@@ -4271,7 +4341,9 @@
       <c r="A155" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B155" s="1"/>
+      <c r="B155" s="1">
+        <v>46247</v>
+      </c>
       <c r="C155" s="2"/>
       <c r="D155" s="6" t="s">
         <v>3</v>
@@ -4284,7 +4356,9 @@
       <c r="A156" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B156" s="1"/>
+      <c r="B156" s="1">
+        <v>46247</v>
+      </c>
       <c r="C156" s="2"/>
       <c r="D156" s="5" t="s">
         <v>3</v>
@@ -4297,7 +4371,9 @@
       <c r="A157" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B157" s="1"/>
+      <c r="B157" s="1">
+        <v>46247</v>
+      </c>
       <c r="C157" s="2"/>
       <c r="D157" s="6" t="s">
         <v>5</v>
@@ -4310,7 +4386,9 @@
       <c r="A158" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B158" s="1"/>
+      <c r="B158" s="1">
+        <v>46247</v>
+      </c>
       <c r="C158" s="2"/>
       <c r="D158" s="5" t="s">
         <v>2</v>
@@ -4323,7 +4401,9 @@
       <c r="A159" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B159" s="1"/>
+      <c r="B159" s="1">
+        <v>46247</v>
+      </c>
       <c r="C159" s="2"/>
       <c r="D159" s="6" t="s">
         <v>4</v>
@@ -4336,7 +4416,9 @@
       <c r="A160" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B160" s="1"/>
+      <c r="B160" s="1">
+        <v>46247</v>
+      </c>
       <c r="C160" s="2"/>
       <c r="D160" s="5" t="s">
         <v>36</v>
@@ -4349,7 +4431,9 @@
       <c r="A161" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B161" s="1"/>
+      <c r="B161" s="1">
+        <v>46247</v>
+      </c>
       <c r="C161" s="2"/>
       <c r="D161" s="6" t="s">
         <v>37</v>
@@ -4362,7 +4446,9 @@
       <c r="A162" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B162" s="1"/>
+      <c r="B162" s="1">
+        <v>46247</v>
+      </c>
       <c r="C162" s="2"/>
       <c r="D162" s="5" t="s">
         <v>36</v>
@@ -4375,7 +4461,9 @@
       <c r="A163" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B163" s="1"/>
+      <c r="B163" s="1">
+        <v>46247</v>
+      </c>
       <c r="C163" s="2"/>
       <c r="D163" s="6" t="s">
         <v>37</v>
@@ -4388,7 +4476,9 @@
       <c r="A164" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B164" s="1"/>
+      <c r="B164" s="1">
+        <v>46247</v>
+      </c>
       <c r="C164" s="2"/>
       <c r="D164" s="5" t="s">
         <v>36</v>
@@ -4401,7 +4491,9 @@
       <c r="A165" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B165" s="1"/>
+      <c r="B165" s="1">
+        <v>46247</v>
+      </c>
       <c r="C165" s="2"/>
       <c r="D165" s="6" t="s">
         <v>37</v>
@@ -4414,7 +4506,9 @@
       <c r="A166" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B166" s="1"/>
+      <c r="B166" s="1">
+        <v>46247</v>
+      </c>
       <c r="C166" s="2"/>
       <c r="D166" s="5" t="s">
         <v>37</v>
@@ -4427,7 +4521,9 @@
       <c r="A167" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B167" s="1"/>
+      <c r="B167" s="1">
+        <v>46247</v>
+      </c>
       <c r="C167" s="2"/>
       <c r="D167" s="6" t="s">
         <v>36</v>
@@ -4440,7 +4536,9 @@
       <c r="A168" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B168" s="1"/>
+      <c r="B168" s="1">
+        <v>46247</v>
+      </c>
       <c r="C168" s="2"/>
       <c r="D168" s="5" t="s">
         <v>3</v>
@@ -4453,7 +4551,9 @@
       <c r="A169" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B169" s="1"/>
+      <c r="B169" s="1">
+        <v>46247</v>
+      </c>
       <c r="C169" s="2"/>
       <c r="D169" s="6" t="s">
         <v>5</v>
@@ -4466,7 +4566,9 @@
       <c r="A170" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B170" s="1"/>
+      <c r="B170" s="1">
+        <v>46247</v>
+      </c>
       <c r="C170" s="2"/>
       <c r="D170" s="5" t="s">
         <v>2</v>
@@ -4479,7 +4581,9 @@
       <c r="A171" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B171" s="1"/>
+      <c r="B171" s="1">
+        <v>46247</v>
+      </c>
       <c r="C171" s="2"/>
       <c r="D171" s="6" t="s">
         <v>4</v>
@@ -4492,7 +4596,9 @@
       <c r="A172" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B172" s="1"/>
+      <c r="B172" s="1">
+        <v>46247</v>
+      </c>
       <c r="C172" s="2"/>
       <c r="D172" s="5" t="s">
         <v>34</v>
@@ -4505,7 +4611,9 @@
       <c r="A173" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B173" s="1"/>
+      <c r="B173" s="1">
+        <v>46247</v>
+      </c>
       <c r="C173" s="2"/>
       <c r="D173" s="6" t="s">
         <v>35</v>
@@ -4518,7 +4626,9 @@
       <c r="A174" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B174" s="1"/>
+      <c r="B174" s="1">
+        <v>46247</v>
+      </c>
       <c r="C174" s="2"/>
       <c r="D174" s="5" t="s">
         <v>5</v>
@@ -4531,7 +4641,9 @@
       <c r="A175" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B175" s="1"/>
+      <c r="B175" s="1">
+        <v>46247</v>
+      </c>
       <c r="C175" s="2"/>
       <c r="D175" s="6" t="s">
         <v>3</v>
@@ -4544,7 +4656,9 @@
       <c r="A176" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B176" s="1"/>
+      <c r="B176" s="1">
+        <v>46247</v>
+      </c>
       <c r="C176" s="2"/>
       <c r="D176" s="5" t="s">
         <v>2</v>
@@ -4557,7 +4671,9 @@
       <c r="A177" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B177" s="1"/>
+      <c r="B177" s="1">
+        <v>46247</v>
+      </c>
       <c r="C177" s="2"/>
       <c r="D177" s="6" t="s">
         <v>4</v>
@@ -4570,7 +4686,9 @@
       <c r="A178" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B178" s="1"/>
+      <c r="B178" s="1">
+        <v>46247</v>
+      </c>
       <c r="C178" s="2"/>
       <c r="D178" s="5" t="s">
         <v>36</v>
@@ -4583,7 +4701,9 @@
       <c r="A179" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B179" s="1"/>
+      <c r="B179" s="1">
+        <v>46247</v>
+      </c>
       <c r="C179" s="2"/>
       <c r="D179" s="6" t="s">
         <v>37</v>
@@ -4596,7 +4716,9 @@
       <c r="A180" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B180" s="1"/>
+      <c r="B180" s="1">
+        <v>46247</v>
+      </c>
       <c r="C180" s="2"/>
       <c r="D180" s="5" t="s">
         <v>2</v>
@@ -4609,7 +4731,9 @@
       <c r="A181" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B181" s="1"/>
+      <c r="B181" s="1">
+        <v>46247</v>
+      </c>
       <c r="C181" s="2"/>
       <c r="D181" s="6" t="s">
         <v>4</v>
@@ -4622,7 +4746,9 @@
       <c r="A182" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B182" s="1"/>
+      <c r="B182" s="1">
+        <v>46247</v>
+      </c>
       <c r="C182" s="2"/>
       <c r="D182" s="5" t="s">
         <v>3</v>
@@ -4635,7 +4761,9 @@
       <c r="A183" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B183" s="1"/>
+      <c r="B183" s="1">
+        <v>46247</v>
+      </c>
       <c r="C183" s="2"/>
       <c r="D183" s="6" t="s">
         <v>5</v>
@@ -4648,7 +4776,9 @@
       <c r="A184" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B184" s="1"/>
+      <c r="B184" s="1">
+        <v>46247</v>
+      </c>
       <c r="C184" s="2"/>
       <c r="D184" s="5" t="s">
         <v>34</v>
@@ -4661,7 +4791,9 @@
       <c r="A185" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B185" s="1"/>
+      <c r="B185" s="1">
+        <v>46247</v>
+      </c>
       <c r="C185" s="2"/>
       <c r="D185" s="6" t="s">
         <v>35</v>
@@ -4674,7 +4806,9 @@
       <c r="A186" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B186" s="1"/>
+      <c r="B186" s="1">
+        <v>46247</v>
+      </c>
       <c r="C186" s="2"/>
       <c r="D186" s="5" t="s">
         <v>4</v>
@@ -4687,7 +4821,9 @@
       <c r="A187" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B187" s="1"/>
+      <c r="B187" s="1">
+        <v>46247</v>
+      </c>
       <c r="C187" s="2"/>
       <c r="D187" s="6" t="s">
         <v>2</v>
@@ -4700,7 +4836,9 @@
       <c r="A188" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B188" s="1"/>
+      <c r="B188" s="1">
+        <v>46247</v>
+      </c>
       <c r="C188" s="2"/>
       <c r="D188" s="5" t="s">
         <v>5</v>
@@ -4713,7 +4851,9 @@
       <c r="A189" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B189" s="1"/>
+      <c r="B189" s="1">
+        <v>46247</v>
+      </c>
       <c r="C189" s="2"/>
       <c r="D189" s="6" t="s">
         <v>3</v>
@@ -4726,7 +4866,9 @@
       <c r="A190" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B190" s="1"/>
+      <c r="B190" s="1">
+        <v>46247</v>
+      </c>
       <c r="C190" s="2"/>
       <c r="D190" s="5" t="s">
         <v>37</v>
@@ -4739,7 +4881,9 @@
       <c r="A191" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B191" s="1"/>
+      <c r="B191" s="1">
+        <v>46247</v>
+      </c>
       <c r="C191" s="2"/>
       <c r="D191" s="6" t="s">
         <v>36</v>
@@ -4752,7 +4896,9 @@
       <c r="A192" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B192" s="1"/>
+      <c r="B192" s="1">
+        <v>46247</v>
+      </c>
       <c r="C192" s="2"/>
       <c r="D192" s="5" t="s">
         <v>34</v>
@@ -4765,7 +4911,9 @@
       <c r="A193" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B193" s="1"/>
+      <c r="B193" s="1">
+        <v>46247</v>
+      </c>
       <c r="C193" s="2"/>
       <c r="D193" s="6" t="s">
         <v>35</v>
@@ -4778,7 +4926,9 @@
       <c r="A194" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B194" s="1"/>
+      <c r="B194" s="1">
+        <v>46247</v>
+      </c>
       <c r="C194" s="2"/>
       <c r="D194" s="5" t="s">
         <v>36</v>
@@ -4791,7 +4941,9 @@
       <c r="A195" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B195" s="1"/>
+      <c r="B195" s="1">
+        <v>46247</v>
+      </c>
       <c r="C195" s="2"/>
       <c r="D195" s="6" t="s">
         <v>37</v>
@@ -4804,7 +4956,9 @@
       <c r="A196" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B196" s="1"/>
+      <c r="B196" s="1">
+        <v>46247</v>
+      </c>
       <c r="C196" s="2"/>
       <c r="D196" s="5" t="s">
         <v>34</v>
@@ -4817,7 +4971,9 @@
       <c r="A197" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B197" s="1"/>
+      <c r="B197" s="1">
+        <v>46247</v>
+      </c>
       <c r="C197" s="2"/>
       <c r="D197" s="6" t="s">
         <v>35</v>
@@ -4830,7 +4986,9 @@
       <c r="A198" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B198" s="1"/>
+      <c r="B198" s="1">
+        <v>46247</v>
+      </c>
       <c r="C198" s="2"/>
       <c r="D198" s="5" t="s">
         <v>34</v>
@@ -4843,7 +5001,9 @@
       <c r="A199" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B199" s="1"/>
+      <c r="B199" s="1">
+        <v>46247</v>
+      </c>
       <c r="C199" s="2"/>
       <c r="D199" s="6" t="s">
         <v>35</v>
@@ -4856,7 +5016,9 @@
       <c r="A200" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B200" s="1"/>
+      <c r="B200" s="1">
+        <v>46247</v>
+      </c>
       <c r="C200" s="2"/>
       <c r="D200" s="5" t="s">
         <v>5</v>
@@ -4869,7 +5031,9 @@
       <c r="A201" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B201" s="1"/>
+      <c r="B201" s="1">
+        <v>46247</v>
+      </c>
       <c r="C201" s="2"/>
       <c r="D201" s="6" t="s">
         <v>3</v>
@@ -4882,7 +5046,9 @@
       <c r="A202" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B202" s="1"/>
+      <c r="B202" s="1">
+        <v>46247</v>
+      </c>
       <c r="C202" s="2"/>
       <c r="D202" s="5" t="s">
         <v>4</v>
@@ -4895,7 +5061,9 @@
       <c r="A203" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B203" s="1"/>
+      <c r="B203" s="1">
+        <v>46247</v>
+      </c>
       <c r="C203" s="2"/>
       <c r="D203" s="6" t="s">
         <v>2</v>
@@ -4908,7 +5076,9 @@
       <c r="A204" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B204" s="1"/>
+      <c r="B204" s="1">
+        <v>46247</v>
+      </c>
       <c r="C204" s="2"/>
       <c r="D204" s="5" t="s">
         <v>34</v>
@@ -4921,7 +5091,9 @@
       <c r="A205" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B205" s="1"/>
+      <c r="B205" s="1">
+        <v>46247</v>
+      </c>
       <c r="C205" s="2"/>
       <c r="D205" s="6" t="s">
         <v>35</v>
@@ -4934,7 +5106,9 @@
       <c r="A206" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B206" s="1"/>
+      <c r="B206" s="1">
+        <v>46247</v>
+      </c>
       <c r="C206" s="2"/>
       <c r="D206" s="5" t="s">
         <v>3</v>
@@ -4947,7 +5121,9 @@
       <c r="A207" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B207" s="1"/>
+      <c r="B207" s="1">
+        <v>46247</v>
+      </c>
       <c r="C207" s="2"/>
       <c r="D207" s="6" t="s">
         <v>4</v>
@@ -4960,7 +5136,9 @@
       <c r="A208" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B208" s="1"/>
+      <c r="B208" s="1">
+        <v>46247</v>
+      </c>
       <c r="C208" s="2"/>
       <c r="D208" s="5" t="s">
         <v>2</v>
@@ -4973,7 +5151,9 @@
       <c r="A209" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B209" s="1"/>
+      <c r="B209" s="1">
+        <v>46247</v>
+      </c>
       <c r="C209" s="2"/>
       <c r="D209" s="6" t="s">
         <v>5</v>
@@ -4986,7 +5166,9 @@
       <c r="A210" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B210" s="1"/>
+      <c r="B210" s="1">
+        <v>46247</v>
+      </c>
       <c r="C210" s="2"/>
       <c r="D210" s="5" t="s">
         <v>34</v>
@@ -4999,7 +5181,9 @@
       <c r="A211" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B211" s="1"/>
+      <c r="B211" s="1">
+        <v>46247</v>
+      </c>
       <c r="C211" s="2"/>
       <c r="D211" s="6" t="s">
         <v>35</v>
@@ -5012,7 +5196,9 @@
       <c r="A212" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B212" s="1"/>
+      <c r="B212" s="1">
+        <v>46247</v>
+      </c>
       <c r="C212" s="2"/>
       <c r="D212" s="5" t="s">
         <v>3</v>
@@ -5025,7 +5211,9 @@
       <c r="A213" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B213" s="1"/>
+      <c r="B213" s="1">
+        <v>46247</v>
+      </c>
       <c r="C213" s="2"/>
       <c r="D213" s="6" t="s">
         <v>5</v>
@@ -5038,7 +5226,9 @@
       <c r="A214" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B214" s="1"/>
+      <c r="B214" s="1">
+        <v>46247</v>
+      </c>
       <c r="C214" s="2"/>
       <c r="D214" s="5" t="s">
         <v>2</v>
@@ -5051,7 +5241,9 @@
       <c r="A215" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B215" s="1"/>
+      <c r="B215" s="1">
+        <v>46247</v>
+      </c>
       <c r="C215" s="2"/>
       <c r="D215" s="6" t="s">
         <v>4</v>
@@ -5064,7 +5256,9 @@
       <c r="A216" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B216" s="1"/>
+      <c r="B216" s="1">
+        <v>46247</v>
+      </c>
       <c r="C216" s="2"/>
       <c r="D216" s="5" t="s">
         <v>34</v>
@@ -5077,7 +5271,9 @@
       <c r="A217" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B217" s="1"/>
+      <c r="B217" s="1">
+        <v>46247</v>
+      </c>
       <c r="C217" s="2"/>
       <c r="D217" s="6" t="s">
         <v>35</v>
@@ -5090,7 +5286,9 @@
       <c r="A218" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B218" s="1"/>
+      <c r="B218" s="1">
+        <v>46247</v>
+      </c>
       <c r="C218" s="2"/>
       <c r="D218" s="5" t="s">
         <v>3</v>
@@ -5103,7 +5301,9 @@
       <c r="A219" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B219" s="1"/>
+      <c r="B219" s="1">
+        <v>46247</v>
+      </c>
       <c r="C219" s="2"/>
       <c r="D219" s="6" t="s">
         <v>5</v>
@@ -5116,7 +5316,9 @@
       <c r="A220" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B220" s="1"/>
+      <c r="B220" s="1">
+        <v>46247</v>
+      </c>
       <c r="C220" s="2"/>
       <c r="D220" s="5" t="s">
         <v>2</v>
@@ -5129,7 +5331,9 @@
       <c r="A221" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B221" s="1"/>
+      <c r="B221" s="1">
+        <v>46247</v>
+      </c>
       <c r="C221" s="2"/>
       <c r="D221" s="6" t="s">
         <v>4</v>
@@ -5142,7 +5346,9 @@
       <c r="A222" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B222" s="1"/>
+      <c r="B222" s="1">
+        <v>46247</v>
+      </c>
       <c r="C222" s="2"/>
       <c r="D222" s="5" t="s">
         <v>36</v>
@@ -5155,7 +5361,9 @@
       <c r="A223" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B223" s="1"/>
+      <c r="B223" s="1">
+        <v>46247</v>
+      </c>
       <c r="C223" s="2"/>
       <c r="D223" s="6" t="s">
         <v>37</v>
@@ -5168,7 +5376,9 @@
       <c r="A224" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B224" s="1"/>
+      <c r="B224" s="1">
+        <v>46247</v>
+      </c>
       <c r="C224" s="2"/>
       <c r="D224" s="5" t="s">
         <v>36</v>
@@ -5181,7 +5391,9 @@
       <c r="A225" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B225" s="1"/>
+      <c r="B225" s="1">
+        <v>46247</v>
+      </c>
       <c r="C225" s="2"/>
       <c r="D225" s="6" t="s">
         <v>37</v>
@@ -5194,7 +5406,9 @@
       <c r="A226" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B226" s="1"/>
+      <c r="B226" s="1">
+        <v>46247</v>
+      </c>
       <c r="C226" s="2"/>
       <c r="D226" s="5" t="s">
         <v>37</v>
@@ -5207,7 +5421,9 @@
       <c r="A227" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B227" s="1"/>
+      <c r="B227" s="1">
+        <v>46247</v>
+      </c>
       <c r="C227" s="2"/>
       <c r="D227" s="6" t="s">
         <v>36</v>
@@ -5220,7 +5436,9 @@
       <c r="A228" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B228" s="1"/>
+      <c r="B228" s="1">
+        <v>46247</v>
+      </c>
       <c r="C228" s="2"/>
       <c r="D228" s="5" t="s">
         <v>36</v>
@@ -5233,7 +5451,9 @@
       <c r="A229" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B229" s="1"/>
+      <c r="B229" s="1">
+        <v>46247</v>
+      </c>
       <c r="C229" s="2"/>
       <c r="D229" s="6" t="s">
         <v>37</v>
